--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_67B2903C1FBE824D7AE39A6D6074A9F5E025DF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98DBC2AD-381F-4429-BE24-CFB5D97960A1}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_0B6A92317CF6C846B8C08174B8F4B2F5E024ECAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8EED24A-136C-493E-81E6-E683052D8E47}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="336">
   <si>
     <t>Run</t>
   </si>
@@ -65,39 +65,753 @@
     <t>SBC</t>
   </si>
   <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Summary of Benefits</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_1.pdf</t>
+  </si>
+  <si>
+    <t>TC002 Molina Gold Core Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_2.pdf</t>
+  </si>
+  <si>
+    <t>TC003 Molina Gold Core 1500 LCS OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500 LCS</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_3.pdf</t>
+  </si>
+  <si>
+    <t>TC004 Molina Silver Core 70 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 70</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_1.pdf</t>
+  </si>
+  <si>
+    <t>TC005 Molina Silver Core Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_2.pdf</t>
+  </si>
+  <si>
+    <t>TC006 Molina Silver Core LCS OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core LCS</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_3.pdf</t>
+  </si>
+  <si>
+    <t>TC007 Molina Silver Core 73 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 73</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_4.pdf</t>
+  </si>
+  <si>
+    <t>TC008 Molina Silver Core 87 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 87</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_5.pdf</t>
+  </si>
+  <si>
+    <t>TC009 Molina Silver Core 94 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 94</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1_6.pdf</t>
+  </si>
+  <si>
+    <t>TC010 Molina Silver Saver 70 with Four Free PCP Visits OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver 70 with Four Free PCP Visits</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_1.pdf</t>
+  </si>
+  <si>
+    <t>TC011 Molina Silver Saver Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_2.pdf</t>
+  </si>
+  <si>
+    <t>TC012 Molina Silver Saver LCS with Four Free PCP Visits OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver LCS with Four Free PCP Visits</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_3.pdf</t>
+  </si>
+  <si>
+    <t>TC013 Molina Silver Saver 73 with Four Free PCP Visits OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver 73 with Four Free PCP Visits</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_4.pdf</t>
+  </si>
+  <si>
+    <t>TC014 Molina Silver Saver 87 with Four Free PCP Visits OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver 87 with Four Free PCP Visits</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_5.pdf</t>
+  </si>
+  <si>
+    <t>TC015 Molina Silver Saver 94 with Four Free PCP Visits OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Saver 94 with Four Free PCP Visits</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S12_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S12_6.pdf</t>
+  </si>
+  <si>
+    <t>TC016 Molina Bronze Saver 7000 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC017 Molina Bronze Saver Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC018 Molina Bronze Saver 7000 LCS OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000 LCS</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC019 Molina Bronze Enhanced 4000 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC020 Molina Bronze Enhanced Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC021 Molina Bronze Enhanced 4000 LCS OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000 LCS</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC022 Molina Gold Enhanced 895 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC023 Molina Gold Enhanced Zero OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced Zero</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC024 Molina Gold Enhanced 895 LCS OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895 LCS</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC025 Molina Silver Empower 2750 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 2750</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S16V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC026 Molina Silver Empower 3750 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 3750</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S17V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S17V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC027 Molina Silver Empower 4500 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 4500</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S18V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S18V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC028 Molina Silver Empower 5500 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 5500</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S19V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S19V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC029 Molina Gold Empower 2000 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Empower 2000</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G16V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC030 Molina Bronze Empower 6000 OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Empower 6000</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B16V_0.pdf</t>
+  </si>
+  <si>
+    <t>TC031 Molina Gold Core 1500 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC032 Molina Gold Core Zero Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core Zero Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC033 Molina Gold Core 1500 LCS Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500 LCS Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC034 Molina Silver Core 70 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 70 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC035 Molina Silver Core Zero Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core Zero Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC036 Molina Silver Core LCS Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core LCS Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC037 Molina Silver Core 73 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 73 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_4.pdf</t>
+  </si>
+  <si>
+    <t>TC038 Molina Silver Core 87 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 87 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_5.pdf</t>
+  </si>
+  <si>
+    <t>TC039 Molina Silver Core 94 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 94 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1V_6.pdf</t>
+  </si>
+  <si>
+    <t>TC040 Molina Bronze Enhanced 4000 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC041 Molina Bronze Enhanced Zero Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced Zero Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC042 Molina Bronze Enhanced 4000 LCS Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000 LCS Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC043 Molina Gold Enhanced 895 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC044 Molina Gold Enhanced Zero Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced Zero Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC045 Molina Gold Enhanced 895 LCS Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895 LCS Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC046 Molina Silver Empower 2750 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 2750 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC047 Molina Silver Empower 3750 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 3750 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC048 Molina Silver Empower 4500 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 4500 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC049 Molina Silver Empower 5500 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 5500 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC050 Molina Gold Empower 2000 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Empower 2000 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC051 Molina Bronze Empower 6000 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Empower 6000 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC052 Molina Bronze Saver 7000 Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000 Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC053 Molina Bronze Saver Zero Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver Zero Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC054 Molina Bronze Saver 7000 LCS Plus with Adult Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000 LCS Plus with Adult Vision</t>
+  </si>
+  <si>
+    <t>TC055 Molina Gold Core 1500 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1DV_1.pdf</t>
+  </si>
+  <si>
+    <t>TC056 Molina Gold Core Zero Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core Zero Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1DV_2.pdf</t>
+  </si>
+  <si>
+    <t>TC057 Molina Gold Core 1500 LCS Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Core 1500 LCS Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1DV_3.pdf</t>
+  </si>
+  <si>
+    <t>TC058 Molina Silver Core 70 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 70 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_1.pdf</t>
+  </si>
+  <si>
+    <t>TC059 Molina Silver Core Zero Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core Zero Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_2.pdf</t>
+  </si>
+  <si>
+    <t>TC060 Molina Silver Core LCS Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core LCS Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_3.pdf</t>
+  </si>
+  <si>
+    <t>TC061 Molina Silver Core 73 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 73 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_4.pdf</t>
+  </si>
+  <si>
+    <t>TC062 Molina Silver Core 87 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 87 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_5.pdf</t>
+  </si>
+  <si>
+    <t>TC063 Molina Silver Core 94 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Core 94 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S1DV_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S1DV_6.pdf</t>
+  </si>
+  <si>
+    <t>TC064 Molina Bronze Saver 7000 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12DV_1.pdf</t>
+  </si>
+  <si>
+    <t>TC065 Molina Bronze Saver Zero Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver Zero Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12DV_2.pdf</t>
+  </si>
+  <si>
+    <t>TC066 Molina Bronze Saver 7000 LCS Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Saver 7000 LCS Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B12DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B12DV_3.pdf</t>
+  </si>
+  <si>
+    <t>TC067 Molina Bronze Enhanced 4000 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10DV_1.pdf</t>
+  </si>
+  <si>
+    <t>TC068 Molina Bronze Enhanced Zero Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced Zero Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10DV_2.pdf</t>
+  </si>
+  <si>
+    <t>TC069 Molina Bronze Enhanced 4000 LCS Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Enhanced 4000 LCS Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B10DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B10DV_3.pdf</t>
+  </si>
+  <si>
+    <t>TC070 Molina Gold Enhanced 895 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9DV_1.pdf</t>
+  </si>
+  <si>
+    <t>TC071 Molina Gold Enhanced Zero Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced Zero Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9DV_2.pdf</t>
+  </si>
+  <si>
+    <t>TC072 Molina Gold Enhanced 895 LCS Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Enhanced 895 LCS Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G9DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G9DV_3.pdf</t>
+  </si>
+  <si>
+    <t>TC073 Molina Silver Empower 2750 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 2750 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC074 Molina Silver Empower 3750 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 3750 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S17DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S17DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC075 Molina Silver Empower 4500 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 4500 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S18DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S18DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC076 Molina Silver Empower 5500 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Empower 5500 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S19DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S19DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC077 Molina Gold Empower 2000 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Gold Empower 2000 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC078 Molina Bronze Empower 6000 Plus with Adult Dental and Vision OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Empower 6000 Plus with Adult Dental and Vision</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>TC079 Molina Bronze Smart Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Smart Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B15_1.pdf</t>
+  </si>
+  <si>
+    <t>TC080 Molina Bronze Smart Zero Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Smart Zero Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B15_2.pdf</t>
+  </si>
+  <si>
+    <t>TC081 Molina Bronze Smart LCS Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Bronze Smart LCS Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_B15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_B15_3.pdf</t>
+  </si>
+  <si>
+    <t>TC082 Molina Silver Smart 70 Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart 70 Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_1.pdf</t>
+  </si>
+  <si>
+    <t>TC083 Molina Silver Smart Zero Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart Zero Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_2.pdf</t>
+  </si>
+  <si>
+    <t>TC084 Molina Silver Smart LCS Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart LCS Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_3.pdf</t>
+  </si>
+  <si>
+    <t>TC085 Molina Silver Smart 73 Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart 73 Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_4.pdf</t>
+  </si>
+  <si>
+    <t>TC086 Molina Silver Smart 87 Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart 87 Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_5.pdf</t>
+  </si>
+  <si>
+    <t>TC087 Molina Silver Smart 94 Heart Health OH-2027</t>
+  </si>
+  <si>
+    <t>Molina Silver Smart 94 Heart Health</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_S15_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_S15_6.pdf</t>
+  </si>
+  <si>
+    <t>SOB</t>
+  </si>
+  <si>
     <t>Marketplace</t>
   </si>
   <si>
-    <t>Summary of Benefits</t>
-  </si>
-  <si>
-    <t>Molina Gold Core 1500</t>
-  </si>
-  <si>
-    <t>https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_1.pdf|https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_1.pdf</t>
-  </si>
-  <si>
-    <t>TC002 Molina Gold Core Zero OH-2027</t>
-  </si>
-  <si>
-    <t>Molina Gold Core Zero</t>
-  </si>
-  <si>
-    <t>https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_2.pdf|https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_2.pdf</t>
-  </si>
-  <si>
-    <t>TC003 Molina Gold Core 1500 LCS OH-2027</t>
-  </si>
-  <si>
-    <t>Molina Gold Core 1500 LCS</t>
-  </si>
-  <si>
-    <t>https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH26SBCE_G1_3.pdf|https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH26SBCS_G1_3.pdf</t>
-  </si>
-  <si>
-    <t>SOB</t>
-  </si>
-  <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1_1.pdf</t>
   </si>
   <si>
@@ -107,15 +821,230 @@
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1_3.pdf</t>
   </si>
   <si>
-    <t>Member</t>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_4.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_5.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_6.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_4.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_5.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_6.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S16V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S17V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S17V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S18V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S18V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S19V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S19V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G16V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B16V_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_4.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_5.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_6.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_4.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_5.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_6.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S17DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S17DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S18DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S18DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S19DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S19DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B16DV_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_4.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_5.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_6.pdf</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -143,8 +1072,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -160,6 +1090,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,44 +1418,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I88"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59.296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="239.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -538,7 +1475,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -550,7 +1487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -567,7 +1504,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -579,9 +1516,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -596,7 +1533,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -608,23 +1545,2464 @@
         <v>23</v>
       </c>
     </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>335</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>335</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>335</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>335</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>335</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>103</v>
+      </c>
+      <c r="I31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>335</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>335</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>112</v>
+      </c>
+      <c r="I34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>335</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>115</v>
+      </c>
+      <c r="I35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>335</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>121</v>
+      </c>
+      <c r="I37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>124</v>
+      </c>
+      <c r="I38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>335</v>
+      </c>
+      <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>127</v>
+      </c>
+      <c r="I39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>335</v>
+      </c>
+      <c r="B40" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>130</v>
+      </c>
+      <c r="I40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>335</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>135</v>
+      </c>
+      <c r="I42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>335</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>137</v>
+      </c>
+      <c r="I43" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>335</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>139</v>
+      </c>
+      <c r="I44" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>335</v>
+      </c>
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>335</v>
+      </c>
+      <c r="B47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>145</v>
+      </c>
+      <c r="I47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>335</v>
+      </c>
+      <c r="B48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
+        <v>147</v>
+      </c>
+      <c r="I48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>335</v>
+      </c>
+      <c r="B49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>149</v>
+      </c>
+      <c r="I49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>335</v>
+      </c>
+      <c r="B50" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>151</v>
+      </c>
+      <c r="I50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>335</v>
+      </c>
+      <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>335</v>
+      </c>
+      <c r="B52" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>155</v>
+      </c>
+      <c r="I52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>335</v>
+      </c>
+      <c r="B53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>157</v>
+      </c>
+      <c r="I53" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>335</v>
+      </c>
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>159</v>
+      </c>
+      <c r="I54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>335</v>
+      </c>
+      <c r="B55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>161</v>
+      </c>
+      <c r="I55" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>163</v>
+      </c>
+      <c r="I56" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>335</v>
+      </c>
+      <c r="B57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>166</v>
+      </c>
+      <c r="I57" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>335</v>
+      </c>
+      <c r="B58" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>169</v>
+      </c>
+      <c r="I58" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>335</v>
+      </c>
+      <c r="B59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>172</v>
+      </c>
+      <c r="I59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>335</v>
+      </c>
+      <c r="B60" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>175</v>
+      </c>
+      <c r="I60" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>335</v>
+      </c>
+      <c r="B61" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>178</v>
+      </c>
+      <c r="I61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>335</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>181</v>
+      </c>
+      <c r="I62" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>184</v>
+      </c>
+      <c r="I63" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>335</v>
+      </c>
+      <c r="B64" t="s">
+        <v>186</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>187</v>
+      </c>
+      <c r="I64" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>335</v>
+      </c>
+      <c r="B65" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>190</v>
+      </c>
+      <c r="I65" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>335</v>
+      </c>
+      <c r="B66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>193</v>
+      </c>
+      <c r="I66" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>335</v>
+      </c>
+      <c r="B67" t="s">
+        <v>195</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>196</v>
+      </c>
+      <c r="I67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>335</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>199</v>
+      </c>
+      <c r="I68" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>335</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>202</v>
+      </c>
+      <c r="I69" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>335</v>
+      </c>
+      <c r="B70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>205</v>
+      </c>
+      <c r="I70" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>335</v>
+      </c>
+      <c r="B71" t="s">
+        <v>207</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>208</v>
+      </c>
+      <c r="I71" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>335</v>
+      </c>
+      <c r="B72" t="s">
+        <v>210</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>211</v>
+      </c>
+      <c r="I72" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" t="s">
+        <v>213</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>214</v>
+      </c>
+      <c r="I73" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>335</v>
+      </c>
+      <c r="B74" t="s">
+        <v>216</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>217</v>
+      </c>
+      <c r="I74" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>335</v>
+      </c>
+      <c r="B75" t="s">
+        <v>219</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>220</v>
+      </c>
+      <c r="I75" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>335</v>
+      </c>
+      <c r="B76" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>335</v>
+      </c>
+      <c r="B77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C77" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>226</v>
+      </c>
+      <c r="I77" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>335</v>
+      </c>
+      <c r="B78" t="s">
+        <v>228</v>
+      </c>
+      <c r="C78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>229</v>
+      </c>
+      <c r="I78" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>335</v>
+      </c>
+      <c r="B79" t="s">
+        <v>231</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>232</v>
+      </c>
+      <c r="I79" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>335</v>
+      </c>
+      <c r="B80" t="s">
+        <v>234</v>
+      </c>
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" t="s">
+        <v>235</v>
+      </c>
+      <c r="I80" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>335</v>
+      </c>
+      <c r="B81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>238</v>
+      </c>
+      <c r="I81" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>335</v>
+      </c>
+      <c r="B82" t="s">
+        <v>240</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>241</v>
+      </c>
+      <c r="I82" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>335</v>
+      </c>
+      <c r="B83" t="s">
+        <v>243</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>244</v>
+      </c>
+      <c r="I83" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>335</v>
+      </c>
+      <c r="B84" t="s">
+        <v>246</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>247</v>
+      </c>
+      <c r="I84" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>335</v>
+      </c>
+      <c r="B85" t="s">
+        <v>249</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>250</v>
+      </c>
+      <c r="I85" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>335</v>
+      </c>
+      <c r="B86" t="s">
+        <v>252</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>253</v>
+      </c>
+      <c r="I86" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>335</v>
+      </c>
+      <c r="B87" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>256</v>
+      </c>
+      <c r="I87" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>335</v>
+      </c>
+      <c r="B88" t="s">
+        <v>258</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>259</v>
+      </c>
+      <c r="I88" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:E4 A2:E2 G2:I2 G3:I4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 B3:I88 B2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="72.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="241.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -641,67 +4019,1489 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>261</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C24" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" t="s">
+        <v>262</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" t="s">
+        <v>262</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" t="s">
+        <v>261</v>
+      </c>
+      <c r="C32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C33" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>261</v>
+      </c>
+      <c r="C34" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" t="s">
+        <v>262</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" t="s">
+        <v>262</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>261</v>
+      </c>
+      <c r="C40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C41" t="s">
+        <v>262</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>261</v>
+      </c>
+      <c r="C44" t="s">
+        <v>262</v>
+      </c>
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C47" t="s">
+        <v>262</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>261</v>
+      </c>
+      <c r="C48" t="s">
+        <v>262</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>148</v>
+      </c>
+      <c r="B49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" t="s">
+        <v>262</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" t="s">
+        <v>261</v>
+      </c>
+      <c r="C51" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" t="s">
+        <v>262</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>261</v>
+      </c>
+      <c r="C55" t="s">
+        <v>262</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" t="s">
+        <v>262</v>
+      </c>
+      <c r="D56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57" t="s">
+        <v>262</v>
+      </c>
+      <c r="D57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" t="s">
+        <v>261</v>
+      </c>
+      <c r="C58" t="s">
+        <v>262</v>
+      </c>
+      <c r="D58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" t="s">
+        <v>261</v>
+      </c>
+      <c r="C59" t="s">
+        <v>262</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" t="s">
+        <v>262</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" t="s">
+        <v>261</v>
+      </c>
+      <c r="C61" t="s">
+        <v>262</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" t="s">
+        <v>261</v>
+      </c>
+      <c r="C62" t="s">
+        <v>262</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" t="s">
+        <v>262</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" t="s">
+        <v>262</v>
+      </c>
+      <c r="D64" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" t="s">
+        <v>261</v>
+      </c>
+      <c r="C65" t="s">
+        <v>262</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>192</v>
+      </c>
+      <c r="B66" t="s">
+        <v>261</v>
+      </c>
+      <c r="C66" t="s">
+        <v>262</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" t="s">
+        <v>261</v>
+      </c>
+      <c r="C67" t="s">
+        <v>262</v>
+      </c>
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68" t="s">
+        <v>261</v>
+      </c>
+      <c r="C68" t="s">
+        <v>262</v>
+      </c>
+      <c r="D68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" t="s">
+        <v>262</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>204</v>
+      </c>
+      <c r="B70" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>207</v>
+      </c>
+      <c r="B71" t="s">
+        <v>261</v>
+      </c>
+      <c r="C71" t="s">
+        <v>262</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>210</v>
+      </c>
+      <c r="B72" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>213</v>
+      </c>
+      <c r="B73" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" t="s">
+        <v>262</v>
+      </c>
+      <c r="D73" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>216</v>
+      </c>
+      <c r="B74" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" t="s">
+        <v>262</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" t="s">
+        <v>262</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>222</v>
+      </c>
+      <c r="B76" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" t="s">
+        <v>262</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" t="s">
+        <v>262</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>228</v>
+      </c>
+      <c r="B78" t="s">
+        <v>261</v>
+      </c>
+      <c r="C78" t="s">
+        <v>262</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>231</v>
+      </c>
+      <c r="B79" t="s">
+        <v>261</v>
+      </c>
+      <c r="C79" t="s">
+        <v>262</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" t="s">
+        <v>262</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>237</v>
+      </c>
+      <c r="B81" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81" t="s">
+        <v>262</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>240</v>
+      </c>
+      <c r="B82" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" t="s">
+        <v>262</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" t="s">
+        <v>261</v>
+      </c>
+      <c r="C83" t="s">
+        <v>262</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>246</v>
+      </c>
+      <c r="B84" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" t="s">
+        <v>262</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>249</v>
+      </c>
+      <c r="B85" t="s">
+        <v>261</v>
+      </c>
+      <c r="C85" t="s">
+        <v>262</v>
+      </c>
+      <c r="D85" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>252</v>
+      </c>
+      <c r="B86" t="s">
+        <v>261</v>
+      </c>
+      <c r="C86" t="s">
+        <v>262</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>255</v>
+      </c>
+      <c r="B87" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" t="s">
+        <v>262</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" t="s">
+        <v>262</v>
+      </c>
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E88" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_E9EF72481E37605E54A31C6A4016A4F540A16DA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C18B1B3-D99B-4BDB-B0C9-7211EF459C6E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_E9EF72481E37605E54A31C6A4016A4F540A16DA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5B12C28-2B7A-4425-83F7-2FE53783087F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5417,9 +5417,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>357</v>
+        <v>9</v>
       </c>
       <c r="B89" t="s">
         <v>261</v>
@@ -6751,7 +6751,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -10057,9 +10057,9 @@
         <v>675</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B249" t="s">
         <v>676</v>
@@ -10086,9 +10086,9 @@
         <v>679</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B250" t="s">
         <v>680</v>
@@ -10115,9 +10115,9 @@
         <v>681</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B251" t="s">
         <v>682</v>
@@ -10144,9 +10144,9 @@
         <v>683</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B252" t="s">
         <v>684</v>
@@ -10173,9 +10173,9 @@
         <v>685</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B253" t="s">
         <v>686</v>
@@ -10202,9 +10202,9 @@
         <v>687</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B254" t="s">
         <v>688</v>
@@ -10231,9 +10231,9 @@
         <v>689</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B255" t="s">
         <v>690</v>
@@ -10260,9 +10260,9 @@
         <v>691</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B256" t="s">
         <v>692</v>
@@ -10289,9 +10289,9 @@
         <v>693</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B257" t="s">
         <v>694</v>
@@ -10318,9 +10318,9 @@
         <v>695</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B258" t="s">
         <v>696</v>
@@ -10347,9 +10347,9 @@
         <v>697</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B259" t="s">
         <v>698</v>
@@ -10376,9 +10376,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B260" t="s">
         <v>700</v>
@@ -10405,9 +10405,9 @@
         <v>701</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B261" t="s">
         <v>702</v>
@@ -10434,9 +10434,9 @@
         <v>703</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B262" t="s">
         <v>704</v>
@@ -10463,9 +10463,9 @@
         <v>705</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B263" t="s">
         <v>706</v>
@@ -10492,9 +10492,9 @@
         <v>707</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B264" t="s">
         <v>708</v>
@@ -10521,9 +10521,9 @@
         <v>709</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B265" t="s">
         <v>710</v>
@@ -10550,9 +10550,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B266" t="s">
         <v>713</v>
@@ -10579,9 +10579,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B267" t="s">
         <v>715</v>
@@ -10608,9 +10608,9 @@
         <v>717</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B268" t="s">
         <v>718</v>
@@ -10637,9 +10637,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B269" t="s">
         <v>720</v>
@@ -10666,9 +10666,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B270" t="s">
         <v>722</v>
@@ -10695,9 +10695,9 @@
         <v>723</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B271" t="s">
         <v>724</v>
@@ -10724,9 +10724,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B272" t="s">
         <v>726</v>
@@ -10753,9 +10753,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B273" t="s">
         <v>728</v>
@@ -10782,9 +10782,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B274" t="s">
         <v>730</v>
@@ -10811,9 +10811,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B275" t="s">
         <v>732</v>
@@ -10840,9 +10840,9 @@
         <v>733</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B276" t="s">
         <v>734</v>
@@ -10869,9 +10869,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B277" t="s">
         <v>736</v>
@@ -10898,9 +10898,9 @@
         <v>737</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B278" t="s">
         <v>738</v>
@@ -10927,9 +10927,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B279" t="s">
         <v>740</v>
@@ -10956,9 +10956,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B280" t="s">
         <v>742</v>
@@ -10985,9 +10985,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B281" t="s">
         <v>744</v>
@@ -11014,9 +11014,9 @@
         <v>745</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B282" t="s">
         <v>746</v>
@@ -11043,9 +11043,9 @@
         <v>748</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B283" t="s">
         <v>749</v>
@@ -11072,9 +11072,9 @@
         <v>751</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B284" t="s">
         <v>752</v>
@@ -11101,9 +11101,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B285" t="s">
         <v>755</v>
@@ -11130,9 +11130,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B286" t="s">
         <v>757</v>
@@ -11159,9 +11159,9 @@
         <v>758</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B287" t="s">
         <v>759</v>
@@ -11188,9 +11188,9 @@
         <v>760</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B288" t="s">
         <v>761</v>
@@ -11217,9 +11217,9 @@
         <v>762</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B289" t="s">
         <v>763</v>
@@ -11246,9 +11246,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B290" t="s">
         <v>765</v>
@@ -11275,9 +11275,9 @@
         <v>766</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B291" t="s">
         <v>767</v>
@@ -11304,9 +11304,9 @@
         <v>768</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B292" t="s">
         <v>769</v>
@@ -11333,9 +11333,9 @@
         <v>770</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B293" t="s">
         <v>771</v>
@@ -11362,9 +11362,9 @@
         <v>772</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B294" t="s">
         <v>773</v>
@@ -11391,9 +11391,9 @@
         <v>774</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B295" t="s">
         <v>775</v>
@@ -11420,9 +11420,9 @@
         <v>777</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B296" t="s">
         <v>778</v>
@@ -11449,9 +11449,9 @@
         <v>779</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B297" t="s">
         <v>780</v>
@@ -11478,9 +11478,9 @@
         <v>781</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B298" t="s">
         <v>782</v>
@@ -11507,9 +11507,9 @@
         <v>783</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B299" t="s">
         <v>784</v>
@@ -11536,9 +11536,9 @@
         <v>785</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B300" t="s">
         <v>786</v>
@@ -11565,9 +11565,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B301" t="s">
         <v>788</v>
@@ -11594,9 +11594,9 @@
         <v>789</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B302" t="s">
         <v>790</v>
@@ -11623,9 +11623,9 @@
         <v>791</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B303" t="s">
         <v>792</v>
@@ -11652,9 +11652,9 @@
         <v>793</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B304" t="s">
         <v>794</v>
@@ -11681,9 +11681,9 @@
         <v>795</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B305" t="s">
         <v>796</v>
@@ -11710,9 +11710,9 @@
         <v>797</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B306" t="s">
         <v>798</v>
@@ -12002,15 +12002,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I315" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
+    <filterColumn colId="2">
       <filters>
-        <filter val="Y"/>
+        <filter val="TX"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I88 A90:I134 B89:I89 A136:I315 B135:I135" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I88 A122:I134 B89:I89 A179:I248 B135:I135 B90:I121 B136:I149 B150:I150 B151:I178 B308:I315 B307:I307 B250:I306 B249:I249" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_70CE30217927462588B21A62D89D467537775006" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE66B700-B1A6-4FED-8420-B8CC9166D3D8}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_70CE30217927462588B21A62D89D467537775006" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B15F36B0-41C2-4005-9C8F-EE767325F417}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plans!A1:I315</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plans!$A$1:$I$315</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -2875,13 +2875,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I315"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="6" max="6" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="241.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2910,7 +2914,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2939,7 +2943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2968,7 +2972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2997,7 +3001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3026,7 +3030,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3055,7 +3059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3084,7 +3088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3113,7 +3117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3142,7 +3146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3171,7 +3175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3229,7 +3233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3258,7 +3262,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -3287,7 +3291,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3316,7 +3320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -3345,7 +3349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -3374,7 +3378,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -3403,7 +3407,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -3432,7 +3436,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -3461,7 +3465,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -3490,7 +3494,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -3519,7 +3523,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -3548,7 +3552,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -3577,7 +3581,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -3635,7 +3639,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -3693,7 +3697,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -3722,7 +3726,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3751,7 +3755,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3780,7 +3784,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -3809,7 +3813,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -3838,7 +3842,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3867,7 +3871,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -3896,7 +3900,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3925,7 +3929,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -3954,7 +3958,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3983,7 +3987,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4012,7 +4016,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4041,7 +4045,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -4070,7 +4074,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -4099,7 +4103,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -4128,7 +4132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -4186,7 +4190,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -4215,7 +4219,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -4244,7 +4248,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -4273,7 +4277,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -4302,7 +4306,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -4331,7 +4335,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -4360,7 +4364,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -4389,7 +4393,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -4418,7 +4422,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -4447,7 +4451,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -4476,7 +4480,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -4505,7 +4509,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -4534,7 +4538,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -4563,7 +4567,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -4592,7 +4596,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4650,7 +4654,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -4679,7 +4683,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4708,7 +4712,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -4737,7 +4741,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -4766,7 +4770,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -4795,7 +4799,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -4853,7 +4857,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -4882,7 +4886,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -4911,7 +4915,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -4940,7 +4944,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -4969,7 +4973,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -4998,7 +5002,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -5027,7 +5031,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -5056,7 +5060,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -5085,7 +5089,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -5114,7 +5118,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -5172,7 +5176,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -5201,7 +5205,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -5230,7 +5234,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -5259,7 +5263,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -5317,7 +5321,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -5346,7 +5350,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -5375,7 +5379,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -5433,7 +5437,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -5491,7 +5495,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -5520,7 +5524,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -5549,7 +5553,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -5578,7 +5582,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -5607,7 +5611,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -5636,7 +5640,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -5665,7 +5669,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -5694,7 +5698,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -5723,7 +5727,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -5752,7 +5756,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -5781,7 +5785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -5810,7 +5814,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -5839,7 +5843,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -5868,7 +5872,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -5897,7 +5901,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -5926,7 +5930,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -5984,7 +5988,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -6013,7 +6017,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -6042,7 +6046,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -6071,7 +6075,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -6129,7 +6133,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -6158,7 +6162,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -6187,7 +6191,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -6216,7 +6220,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -6245,7 +6249,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -6274,7 +6278,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -6303,7 +6307,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -6332,7 +6336,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -6361,7 +6365,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -6390,7 +6394,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -6419,7 +6423,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -6448,7 +6452,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -6477,7 +6481,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -6506,7 +6510,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -6535,7 +6539,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -6564,7 +6568,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -6593,7 +6597,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -6651,7 +6655,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -6709,7 +6713,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -6738,7 +6742,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -6767,7 +6771,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -6796,7 +6800,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -6825,7 +6829,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -6854,7 +6858,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -6883,7 +6887,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -6941,7 +6945,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -6970,7 +6974,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -6999,7 +7003,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -7028,7 +7032,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -7057,7 +7061,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -7086,7 +7090,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -7115,7 +7119,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -7144,7 +7148,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -7173,7 +7177,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>9</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>9</v>
       </c>
@@ -7231,7 +7235,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>9</v>
       </c>
@@ -7260,7 +7264,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -7318,7 +7322,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -7347,7 +7351,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -7376,7 +7380,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -7405,7 +7409,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -7434,7 +7438,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -7463,7 +7467,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>9</v>
       </c>
@@ -7492,7 +7496,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -7521,7 +7525,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>9</v>
       </c>
@@ -7550,7 +7554,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -7579,7 +7583,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -7608,7 +7612,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>9</v>
       </c>
@@ -7637,7 +7641,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -7666,7 +7670,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -7724,7 +7728,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>9</v>
       </c>
@@ -7753,7 +7757,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>9</v>
       </c>
@@ -7782,7 +7786,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>9</v>
       </c>
@@ -7811,7 +7815,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -7840,7 +7844,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -7869,7 +7873,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>9</v>
       </c>
@@ -7898,7 +7902,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>9</v>
       </c>
@@ -7927,7 +7931,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -7985,7 +7989,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -8014,7 +8018,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -8043,7 +8047,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>9</v>
       </c>
@@ -8072,7 +8076,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -8101,7 +8105,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -8130,7 +8134,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -8159,7 +8163,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -8188,7 +8192,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -8217,7 +8221,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -8246,7 +8250,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -8304,7 +8308,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>9</v>
       </c>
@@ -8333,7 +8337,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -8391,7 +8395,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -8420,7 +8424,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -8449,7 +8453,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -8478,7 +8482,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -8507,7 +8511,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -8536,7 +8540,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -8565,7 +8569,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -8594,7 +8598,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>9</v>
       </c>
@@ -8652,7 +8656,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>9</v>
       </c>
@@ -8681,7 +8685,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -8710,7 +8714,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -8739,7 +8743,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -8768,7 +8772,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -8797,7 +8801,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -8826,7 +8830,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -8855,7 +8859,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -8884,7 +8888,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -8913,7 +8917,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -8942,7 +8946,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -8971,7 +8975,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -9000,7 +9004,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -9029,7 +9033,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -9058,7 +9062,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -9087,7 +9091,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -9116,7 +9120,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -9145,7 +9149,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -9174,7 +9178,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -9203,7 +9207,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -9232,7 +9236,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -9261,7 +9265,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -9319,7 +9323,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -9348,7 +9352,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -9377,7 +9381,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -9406,7 +9410,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -9435,7 +9439,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>9</v>
       </c>
@@ -9464,7 +9468,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>9</v>
       </c>
@@ -9493,7 +9497,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>9</v>
       </c>
@@ -9551,7 +9555,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>9</v>
       </c>
@@ -9580,7 +9584,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -9609,7 +9613,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>9</v>
       </c>
@@ -9638,7 +9642,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -9667,7 +9671,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>9</v>
       </c>
@@ -9696,7 +9700,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>9</v>
       </c>
@@ -9725,7 +9729,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>9</v>
       </c>
@@ -9754,7 +9758,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>9</v>
       </c>
@@ -9783,7 +9787,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>9</v>
       </c>
@@ -9812,7 +9816,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>9</v>
       </c>
@@ -9841,7 +9845,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>9</v>
       </c>
@@ -9870,7 +9874,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>9</v>
       </c>
@@ -9899,7 +9903,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -9928,7 +9932,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>9</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>9</v>
       </c>
@@ -9986,7 +9990,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -10015,7 +10019,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>9</v>
       </c>
@@ -10044,7 +10048,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>9</v>
       </c>
@@ -10073,7 +10077,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>9</v>
       </c>
@@ -10102,7 +10106,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>9</v>
       </c>
@@ -10131,7 +10135,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>9</v>
       </c>
@@ -10160,7 +10164,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -10189,7 +10193,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>9</v>
       </c>
@@ -10218,7 +10222,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>9</v>
       </c>
@@ -10247,7 +10251,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>9</v>
       </c>
@@ -10276,7 +10280,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>9</v>
       </c>
@@ -10305,7 +10309,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>9</v>
       </c>
@@ -10334,7 +10338,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>9</v>
       </c>
@@ -10363,7 +10367,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>9</v>
       </c>
@@ -10392,7 +10396,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>9</v>
       </c>
@@ -10421,7 +10425,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -10450,7 +10454,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>9</v>
       </c>
@@ -10479,7 +10483,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>9</v>
       </c>
@@ -10508,7 +10512,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>9</v>
       </c>
@@ -10537,7 +10541,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>9</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>9</v>
       </c>
@@ -10595,7 +10599,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>9</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>9</v>
       </c>
@@ -10653,7 +10657,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>9</v>
       </c>
@@ -10682,7 +10686,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -10711,7 +10715,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>9</v>
       </c>
@@ -10740,7 +10744,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>9</v>
       </c>
@@ -10769,7 +10773,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>9</v>
       </c>
@@ -10798,7 +10802,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>9</v>
       </c>
@@ -10827,7 +10831,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>9</v>
       </c>
@@ -10856,7 +10860,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>9</v>
       </c>
@@ -10885,7 +10889,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>9</v>
       </c>
@@ -10914,7 +10918,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>9</v>
       </c>
@@ -10943,7 +10947,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -10972,7 +10976,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>9</v>
       </c>
@@ -11001,7 +11005,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>9</v>
       </c>
@@ -11030,7 +11034,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>9</v>
       </c>
@@ -11059,7 +11063,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>9</v>
       </c>
@@ -11088,7 +11092,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>9</v>
       </c>
@@ -11117,7 +11121,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>9</v>
       </c>
@@ -11146,7 +11150,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>9</v>
       </c>
@@ -11175,7 +11179,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>9</v>
       </c>
@@ -11204,7 +11208,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -11233,7 +11237,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>9</v>
       </c>
@@ -11262,7 +11266,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>9</v>
       </c>
@@ -11291,7 +11295,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>9</v>
       </c>
@@ -11320,7 +11324,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>9</v>
       </c>
@@ -11349,7 +11353,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>9</v>
       </c>
@@ -11378,7 +11382,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>9</v>
       </c>
@@ -11407,7 +11411,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>9</v>
       </c>
@@ -11436,7 +11440,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>9</v>
       </c>
@@ -11465,7 +11469,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -11494,7 +11498,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>9</v>
       </c>
@@ -11523,7 +11527,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>9</v>
       </c>
@@ -11552,7 +11556,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>9</v>
       </c>
@@ -11581,7 +11585,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>9</v>
       </c>
@@ -11610,7 +11614,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>9</v>
       </c>
@@ -11639,7 +11643,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>9</v>
       </c>
@@ -11668,7 +11672,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>9</v>
       </c>
@@ -11697,7 +11701,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>9</v>
       </c>
@@ -11726,7 +11730,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -11755,9 +11759,9 @@
         <v>798</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B307" t="s">
         <v>800</v>
@@ -11784,9 +11788,9 @@
         <v>802</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B308" t="s">
         <v>803</v>
@@ -11813,9 +11817,9 @@
         <v>804</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B309" t="s">
         <v>805</v>
@@ -11842,9 +11846,9 @@
         <v>806</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B310" t="s">
         <v>807</v>
@@ -11871,9 +11875,9 @@
         <v>808</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B311" t="s">
         <v>809</v>
@@ -11900,7 +11904,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>799</v>
       </c>
@@ -11929,7 +11933,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>799</v>
       </c>
@@ -11958,9 +11962,9 @@
         <v>814</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B314" t="s">
         <v>815</v>
@@ -11987,9 +11991,9 @@
         <v>816</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>799</v>
+        <v>9</v>
       </c>
       <c r="B315" t="s">
         <v>817</v>
@@ -12017,10 +12021,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I315" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I315" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="NV"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I315" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I306 A312:I313 B307:I307 B308:I311 B315:I315 B314:I314" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12028,14 +12038,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="48.796875" customWidth="1"/>
     <col min="3" max="3" width="110.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>819</v>
       </c>
@@ -12046,7 +12056,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>822</v>
       </c>

--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_70CE30217927462588B21A62D89D467537775006" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B15F36B0-41C2-4005-9C8F-EE767325F417}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_0CF6D607091F0106E0C21E1DAC55B2F500AFEF90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE2160D-FC22-4D66-A833-FA0CD05814D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
     <t>Schedule of Benefits</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1_1.pdf</t>
@@ -83,7 +83,7 @@
     <t>TC002 Molina Gold Core Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core Zero</t>
+    <t>Schedule of Benefits – Molina Gold Core Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1_2.pdf</t>
@@ -92,7 +92,7 @@
     <t>TC003 Molina Gold Core 1500 LCS OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500 LCS</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1_3.pdf</t>
@@ -101,7 +101,7 @@
     <t>TC004 Molina Silver Core 70 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 70</t>
+    <t>Schedule of Benefits – Molina Silver Core 70</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_1.pdf</t>
@@ -110,7 +110,7 @@
     <t>TC005 Molina Silver Core Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core Zero</t>
+    <t>Schedule of Benefits – Molina Silver Core Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_2.pdf</t>
@@ -119,7 +119,7 @@
     <t>TC006 Molina Silver Core LCS OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core LCS</t>
+    <t>Schedule of Benefits – Molina Silver Core LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_3.pdf</t>
@@ -128,7 +128,7 @@
     <t>TC007 Molina Silver Core 73 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 73</t>
+    <t>Schedule of Benefits – Molina Silver Core 73</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_4.pdf</t>
@@ -137,7 +137,7 @@
     <t>TC008 Molina Silver Core 87 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 87</t>
+    <t>Schedule of Benefits – Molina Silver Core 87</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_5.pdf</t>
@@ -146,7 +146,7 @@
     <t>TC009 Molina Silver Core 94 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 94</t>
+    <t>Schedule of Benefits – Molina Silver Core 94</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1_6.pdf</t>
@@ -155,7 +155,7 @@
     <t>TC010 Molina Silver Saver 70 with Four Free PCP Visits OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 70 with Four Free PCP Visits</t>
+    <t>Schedule of Benefits – Molina Silver Saver 70 with Four Free PCP Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_1.pdf</t>
@@ -164,7 +164,7 @@
     <t>TC011 Molina Silver Saver Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver Zero</t>
+    <t>Schedule of Benefits – Molina Silver Saver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_2.pdf</t>
@@ -173,7 +173,7 @@
     <t>TC012 Molina Silver Saver LCS with Four Free PCP Visits OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver LCS with Four Free PCP Visits</t>
+    <t>Schedule of Benefits – Molina Silver Saver LCS with Four Free PCP Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_3.pdf</t>
@@ -182,7 +182,7 @@
     <t>TC013 Molina Silver Saver 73 with Four Free PCP Visits OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 73 with Four Free PCP Visits</t>
+    <t>Schedule of Benefits – Molina Silver Saver 73 with Four Free PCP Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_4.pdf</t>
@@ -191,7 +191,7 @@
     <t>TC014 Molina Silver Saver 87 with Four Free PCP Visits OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 87 with Four Free PCP Visits</t>
+    <t>Schedule of Benefits – Molina Silver Saver 87 with Four Free PCP Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_5.pdf</t>
@@ -200,7 +200,7 @@
     <t>TC015 Molina Silver Saver 94 with Four Free PCP Visits OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 94 with Four Free PCP Visits</t>
+    <t>Schedule of Benefits – Molina Silver Saver 94 with Four Free PCP Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S12_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S12_6.pdf</t>
@@ -209,7 +209,7 @@
     <t>TC016 Molina Bronze Saver 7000 OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_1.pdf</t>
@@ -218,7 +218,7 @@
     <t>TC017 Molina Bronze Saver Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver Zero</t>
+    <t>Schedule of Benefits – Molina Bronze Saver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_2.pdf</t>
@@ -227,7 +227,7 @@
     <t>TC018 Molina Bronze Saver 7000 LCS OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 LCS</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12V_3.pdf</t>
@@ -236,7 +236,7 @@
     <t>TC019 Molina Bronze Enhanced 4000 OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_1.pdf</t>
@@ -245,7 +245,7 @@
     <t>TC020 Molina Bronze Enhanced Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced Zero</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_2.pdf</t>
@@ -254,7 +254,7 @@
     <t>TC021 Molina Bronze Enhanced 4000 LCS OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000 LCS</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10V_3.pdf</t>
@@ -263,7 +263,7 @@
     <t>TC022 Molina Gold Enhanced 895 OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_1.pdf</t>
@@ -272,7 +272,7 @@
     <t>TC023 Molina Gold Enhanced Zero OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced Zero</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_2.pdf</t>
@@ -281,7 +281,7 @@
     <t>TC024 Molina Gold Enhanced 895 LCS OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895 LCS</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9V_3.pdf</t>
@@ -290,7 +290,7 @@
     <t>TC025 Molina Silver Empower 2750 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 2750</t>
+    <t>Schedule of Benefits – Molina Silver Empower 2750</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S16V_0.pdf</t>
@@ -299,7 +299,7 @@
     <t>TC026 Molina Silver Empower 3750 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 3750</t>
+    <t>Schedule of Benefits – Molina Silver Empower 3750</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S17V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S17V_0.pdf</t>
@@ -308,7 +308,7 @@
     <t>TC027 Molina Silver Empower 4500 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 4500</t>
+    <t>Schedule of Benefits – Molina Silver Empower 4500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S18V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S18V_0.pdf</t>
@@ -317,7 +317,7 @@
     <t>TC028 Molina Silver Empower 5500 OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 5500</t>
+    <t>Schedule of Benefits – Molina Silver Empower 5500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S19V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S19V_0.pdf</t>
@@ -326,7 +326,7 @@
     <t>TC029 Molina Gold Empower 2000 OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Empower 2000</t>
+    <t>Schedule of Benefits – Molina Gold Empower 2000</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G16V_0.pdf</t>
@@ -335,7 +335,7 @@
     <t>TC030 Molina Bronze Empower 6000 OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Empower 6000</t>
+    <t>Schedule of Benefits – Molina Bronze Empower 6000</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B16V_0.pdf</t>
@@ -344,7 +344,7 @@
     <t>TC031 Molina Gold Core 1500 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_1.pdf</t>
@@ -353,7 +353,7 @@
     <t>TC032 Molina Gold Core Zero Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_2.pdf</t>
@@ -362,7 +362,7 @@
     <t>TC033 Molina Gold Core 1500 LCS Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1V_3.pdf</t>
@@ -371,7 +371,7 @@
     <t>TC034 Molina Silver Core 70 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 70 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 70 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_1.pdf</t>
@@ -380,7 +380,7 @@
     <t>TC035 Molina Silver Core Zero Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_2.pdf</t>
@@ -389,7 +389,7 @@
     <t>TC036 Molina Silver Core LCS Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_3.pdf</t>
@@ -398,7 +398,7 @@
     <t>TC037 Molina Silver Core 73 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 73 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 73 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_4.pdf</t>
@@ -407,7 +407,7 @@
     <t>TC038 Molina Silver Core 87 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 87 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 87 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_5.pdf</t>
@@ -416,7 +416,7 @@
     <t>TC039 Molina Silver Core 94 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 94 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 94 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1V_6.pdf</t>
@@ -425,97 +425,97 @@
     <t>TC040 Molina Bronze Enhanced 4000 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC041 Molina Bronze Enhanced Zero Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC042 Molina Bronze Enhanced 4000 LCS Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC043 Molina Gold Enhanced 895 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC044 Molina Gold Enhanced Zero Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC045 Molina Gold Enhanced 895 LCS Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC046 Molina Silver Empower 2750 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 2750 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 2750 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC047 Molina Silver Empower 3750 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 3750 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 3750 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC048 Molina Silver Empower 4500 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 4500 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 4500 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC049 Molina Silver Empower 5500 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 5500 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 5500 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC050 Molina Gold Empower 2000 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Empower 2000 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Empower 2000 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC051 Molina Bronze Empower 6000 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Empower 6000 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Empower 6000 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC052 Molina Bronze Saver 7000 Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC053 Molina Bronze Saver Zero Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC054 Molina Bronze Saver 7000 LCS Plus with Adult Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>TC055 Molina Gold Core 1500 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_1.pdf</t>
@@ -524,7 +524,7 @@
     <t>TC056 Molina Gold Core Zero Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core Zero Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core Zero Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_2.pdf</t>
@@ -533,7 +533,7 @@
     <t>TC057 Molina Gold Core 1500 LCS Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Core 1500 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Core 1500 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G1DV_3.pdf</t>
@@ -542,7 +542,7 @@
     <t>TC058 Molina Silver Core 70 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 70 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 70 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_1.pdf</t>
@@ -551,7 +551,7 @@
     <t>TC059 Molina Silver Core Zero Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core Zero Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core Zero Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_2.pdf</t>
@@ -560,7 +560,7 @@
     <t>TC060 Molina Silver Core LCS Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_3.pdf</t>
@@ -569,7 +569,7 @@
     <t>TC061 Molina Silver Core 73 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 73 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 73 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_4.pdf</t>
@@ -578,7 +578,7 @@
     <t>TC062 Molina Silver Core 87 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 87 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 87 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_5.pdf</t>
@@ -587,7 +587,7 @@
     <t>TC063 Molina Silver Core 94 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 94 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 94 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S1DV_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S1DV_6.pdf</t>
@@ -596,7 +596,7 @@
     <t>TC064 Molina Bronze Saver 7000 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_1.pdf</t>
@@ -605,7 +605,7 @@
     <t>TC065 Molina Bronze Saver Zero Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver Zero Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver Zero Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_2.pdf</t>
@@ -614,7 +614,7 @@
     <t>TC066 Molina Bronze Saver 7000 LCS Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B12DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B12DV_3.pdf</t>
@@ -623,7 +623,7 @@
     <t>TC067 Molina Bronze Enhanced 4000 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_1.pdf</t>
@@ -632,7 +632,7 @@
     <t>TC068 Molina Bronze Enhanced Zero Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced Zero Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced Zero Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_2.pdf</t>
@@ -641,7 +641,7 @@
     <t>TC069 Molina Bronze Enhanced 4000 LCS Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Enhanced 4000 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Enhanced 4000 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B10DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B10DV_3.pdf</t>
@@ -650,7 +650,7 @@
     <t>TC070 Molina Gold Enhanced 895 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_1.pdf</t>
@@ -659,7 +659,7 @@
     <t>TC071 Molina Gold Enhanced Zero Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced Zero Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced Zero Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_2.pdf</t>
@@ -668,7 +668,7 @@
     <t>TC072 Molina Gold Enhanced 895 LCS Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 895 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 895 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G9DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G9DV_3.pdf</t>
@@ -677,7 +677,7 @@
     <t>TC073 Molina Silver Empower 2750 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 2750 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 2750 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S16DV_0.pdf</t>
@@ -686,7 +686,7 @@
     <t>TC074 Molina Silver Empower 3750 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 3750 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 3750 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S17DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S17DV_0.pdf</t>
@@ -695,7 +695,7 @@
     <t>TC075 Molina Silver Empower 4500 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 4500 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 4500 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S18DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S18DV_0.pdf</t>
@@ -704,7 +704,7 @@
     <t>TC076 Molina Silver Empower 5500 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Empower 5500 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Empower 5500 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S19DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S19DV_0.pdf</t>
@@ -713,7 +713,7 @@
     <t>TC077 Molina Gold Empower 2000 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Gold Empower 2000 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Empower 2000 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_G16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_G16DV_0.pdf</t>
@@ -722,7 +722,7 @@
     <t>TC078 Molina Bronze Empower 6000 Plus with Adult Dental and Vision OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Empower 6000 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Bronze Empower 6000 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B16DV_0.pdf</t>
@@ -731,7 +731,7 @@
     <t>TC079 Molina Bronze Smart Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Smart Heart Health</t>
+    <t>Schedule of Benefits – Molina Bronze Smart Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_1.pdf</t>
@@ -740,7 +740,7 @@
     <t>TC080 Molina Bronze Smart Zero Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Smart Zero Heart Health</t>
+    <t>Schedule of Benefits – Molina Bronze Smart Zero Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_2.pdf</t>
@@ -749,7 +749,7 @@
     <t>TC081 Molina Bronze Smart LCS Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Smart LCS Heart Health</t>
+    <t>Schedule of Benefits – Molina Bronze Smart LCS Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_B15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_B15_3.pdf</t>
@@ -758,7 +758,7 @@
     <t>TC082 Molina Silver Smart 70 Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart 70 Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart 70 Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_1.pdf</t>
@@ -767,7 +767,7 @@
     <t>TC083 Molina Silver Smart Zero Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart Zero Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart Zero Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_2.pdf</t>
@@ -776,7 +776,7 @@
     <t>TC084 Molina Silver Smart LCS Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart LCS Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart LCS Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_3.pdf</t>
@@ -785,7 +785,7 @@
     <t>TC085 Molina Silver Smart 73 Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart 73 Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart 73 Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_4.pdf</t>
@@ -794,7 +794,7 @@
     <t>TC086 Molina Silver Smart 87 Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart 87 Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart 87 Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_5.pdf</t>
@@ -803,7 +803,7 @@
     <t>TC087 Molina Silver Smart 94 Heart Health OH-2027</t>
   </si>
   <si>
-    <t>Molina Silver Smart 94 Heart Health</t>
+    <t>Schedule of Benefits – Molina Silver Smart 94 Heart Health</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH26SOBE_S15_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH26SOBS_S15_6.pdf</t>
@@ -1016,7 +1016,7 @@
     <t>CA</t>
   </si>
   <si>
-    <t>Bronze 60 HMO</t>
+    <t>Schedule of Benefits – Bronze 60 HMO</t>
   </si>
   <si>
     <t>https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ca/materials/SOB/2027/english/CA27SOBE_B60_1.pdf|https://pws-q3.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ca/materials/SOB/2027/spanish/CA27SOBS_B60_1.pdf</t>
@@ -1025,7 +1025,7 @@
     <t>TC122 $0 Cost Share HMO AI-AN CA-2027</t>
   </si>
   <si>
-    <t>$0 Cost Share HMO AI-AN</t>
+    <t>Schedule of Benefits – $0 Cost Share HMO AI-AN</t>
   </si>
   <si>
     <t/>
@@ -1034,67 +1034,67 @@
     <t>TC123 Bronze 60 HMO AI-AN CA-2027</t>
   </si>
   <si>
-    <t>Bronze 60 HMO AI-AN</t>
+    <t>Schedule of Benefits – Bronze 60 HMO AI-AN</t>
   </si>
   <si>
     <t>TC124 Gold 80 HMO CA-2027</t>
   </si>
   <si>
-    <t>Gold 80 HMO</t>
+    <t>Schedule of Benefits – Gold 80 HMO</t>
   </si>
   <si>
     <t>TC125 Gold 80 HMO AI-AN CA-2027</t>
   </si>
   <si>
-    <t>Gold 80 HMO AI-AN</t>
+    <t>Schedule of Benefits – Gold 80 HMO AI-AN</t>
   </si>
   <si>
     <t>TC126 Minimum Coverage HMO CA-2027</t>
   </si>
   <si>
-    <t>Minimum Coverage HMO</t>
+    <t>Schedule of Benefits – Minimum Coverage HMO</t>
   </si>
   <si>
     <t>TC127 Platinum 90 HMO CA-2027</t>
   </si>
   <si>
-    <t>Platinum 90 HMO</t>
+    <t>Schedule of Benefits – Platinum 90 HMO</t>
   </si>
   <si>
     <t>TC128 Platinum 90 HMO AI-AN CA-2027</t>
   </si>
   <si>
-    <t>Platinum 90 HMO AI-AN</t>
+    <t>Schedule of Benefits – Platinum 90 HMO AI-AN</t>
   </si>
   <si>
     <t>TC129 Silver 70 HMO CA-2027</t>
   </si>
   <si>
-    <t>Silver 70 HMO</t>
+    <t>Schedule of Benefits – Silver 70 HMO</t>
   </si>
   <si>
     <t>TC130 Silver 70 HMO AI-AN CA-2027</t>
   </si>
   <si>
-    <t>Silver 70 HMO AI-AN</t>
+    <t>Schedule of Benefits – Silver 70 HMO AI-AN</t>
   </si>
   <si>
     <t>TC131 Silver 73 HMO CA-2027</t>
   </si>
   <si>
-    <t>Silver 73 HMO</t>
+    <t>Schedule of Benefits – Silver 73 HMO</t>
   </si>
   <si>
     <t>TC132 Silver 87 HMO CA-2027</t>
   </si>
   <si>
-    <t>Silver 87 HMO</t>
+    <t>Schedule of Benefits – Silver 87 HMO</t>
   </si>
   <si>
     <t>TC133 Silver 94 HMO CA-2027</t>
   </si>
   <si>
-    <t>Silver 94 HMO</t>
+    <t>Schedule of Benefits – Silver 94 HMO</t>
   </si>
   <si>
     <t>TC134 Molina Cascade Complete Gold WA-2027</t>
@@ -1103,7 +1103,7 @@
     <t>WA</t>
   </si>
   <si>
-    <t>Molina Cascade Complete Gold</t>
+    <t>Schedule of Benefits – Molina Cascade Complete Gold</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G6_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G6_1.pdf</t>
@@ -1112,7 +1112,7 @@
     <t>TC135 Molina Cascade Complete Gold Zero WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Complete Gold Zero</t>
+    <t>Schedule of Benefits – Molina Cascade Complete Gold Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G6_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G6_2.pdf</t>
@@ -1121,7 +1121,7 @@
     <t>TC136 Molina Cascade Complete Gold LCS WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Complete Gold LCS</t>
+    <t>Schedule of Benefits – Molina Cascade Complete Gold LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G6_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G6_3.pdf</t>
@@ -1130,7 +1130,7 @@
     <t>TC137 Molina Cascade Silver 70 WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver 70</t>
+    <t>Schedule of Benefits – Molina Cascade Silver 70</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_1.pdf</t>
@@ -1139,7 +1139,7 @@
     <t>TC138 Molina Cascade Silver Zero WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver Zero</t>
+    <t>Schedule of Benefits – Molina Cascade Silver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_2.pdf</t>
@@ -1148,7 +1148,7 @@
     <t>TC139 Molina Cascade Silver LCS WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver LCS</t>
+    <t>Schedule of Benefits – Molina Cascade Silver LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_3.pdf</t>
@@ -1157,7 +1157,7 @@
     <t>TC140 Molina Cascade Silver 73 WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver 73</t>
+    <t>Schedule of Benefits – Molina Cascade Silver 73</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_4.pdf</t>
@@ -1166,7 +1166,7 @@
     <t>TC141 Molina Cascade Silver 87 WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver 87</t>
+    <t>Schedule of Benefits – Molina Cascade Silver 87</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_5.pdf</t>
@@ -1175,7 +1175,7 @@
     <t>TC142 Molina Cascade Silver 94 WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Silver 94</t>
+    <t>Schedule of Benefits – Molina Cascade Silver 94</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_S6_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_S6_6.pdf</t>
@@ -1184,7 +1184,7 @@
     <t>TC143 Molina Cascade Bronze WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Bronze</t>
+    <t>Schedule of Benefits – Molina Cascade Bronze</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_B6_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_B6_1.pdf</t>
@@ -1193,7 +1193,7 @@
     <t>TC144 Molina Cascade Bronze Zero WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Bronze Zero</t>
+    <t>Schedule of Benefits – Molina Cascade Bronze Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_B6_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_B6_2.pdf</t>
@@ -1202,7 +1202,7 @@
     <t>TC145 Molina Cascade Bronze LCS WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Bronze LCS</t>
+    <t>Schedule of Benefits – Molina Cascade Bronze LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_B6_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_B6_3.pdf</t>
@@ -1211,7 +1211,7 @@
     <t>TC146 Molina Cascade Vital Gold WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Vital Gold</t>
+    <t>Schedule of Benefits – Molina Cascade Vital Gold</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G7_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G7_1.pdf</t>
@@ -1220,7 +1220,7 @@
     <t>TC147 Molina Cascade Vital Gold Zero WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Vital Gold Zero</t>
+    <t>Schedule of Benefits – Molina Cascade Vital Gold Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G7_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G7_2.pdf</t>
@@ -1229,7 +1229,7 @@
     <t>TC148 Molina Cascade Vital Gold LCS WA-2027</t>
   </si>
   <si>
-    <t>Molina Cascade Vital Gold LCS</t>
+    <t>Schedule of Benefits – Molina Cascade Vital Gold LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/english/WA27SOBE_G7_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/wa/materials/SOB/2027/spanish/WA27SOBS_G7_3.pdf</t>
@@ -1241,7 +1241,7 @@
     <t>NM</t>
   </si>
   <si>
-    <t>Molina Gold Saver On Exchange</t>
+    <t>Schedule of Benefits – Molina Gold Saver On Exchange</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G1_1.pdf</t>
@@ -1250,7 +1250,7 @@
     <t>TC150 Molina Native American Gold Saver Zero NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Gold Saver Zero</t>
+    <t>Schedule of Benefits – Molina Native American Gold Saver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G1_2.pdf</t>
@@ -1259,7 +1259,7 @@
     <t>TC151 Molina Native American Gold Saver LCS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Gold Saver LCS</t>
+    <t>Schedule of Benefits – Molina Native American Gold Saver LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G1_3.pdf</t>
@@ -1268,7 +1268,7 @@
     <t>TC152 Molina Native American Gold Saver Turquoise 3 LCS EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Gold Saver Turquoise 3 LCS EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Native American Gold Saver Turquoise 3 LCS EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G1_13.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G1_13.pdf</t>
@@ -1277,7 +1277,7 @@
     <t>TC153 Molina Gold Saver Turquoise 3 EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Gold Saver Turquoise 3 EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Gold Saver Turquoise 3 EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G1_90.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G1_90.pdf</t>
@@ -1286,7 +1286,7 @@
     <t>TC154 Molina Clear Cost Gold On Exchange NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Gold On Exchange</t>
+    <t>Schedule of Benefits – Molina Clear Cost Gold On Exchange</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G13_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G13_1.pdf</t>
@@ -1295,7 +1295,7 @@
     <t>TC155 Molina Native American Clear Cost Gold Zero NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Clear Cost Gold Zero</t>
+    <t>Schedule of Benefits – Molina Native American Clear Cost Gold Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G13_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G13_2.pdf</t>
@@ -1304,7 +1304,7 @@
     <t>TC156 Molina Native American Clear Cost Gold LCS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Clear Cost Gold LCS</t>
+    <t>Schedule of Benefits – Molina Native American Clear Cost Gold LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G13_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G13_3.pdf</t>
@@ -1313,7 +1313,7 @@
     <t>TC157 Molina Native American Clear Cost Turquoise 3 LCS EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Clear Cost Turquoise 3 LCS EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Native American Clear Cost Turquoise 3 LCS EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G13_13.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G13_13.pdf</t>
@@ -1322,7 +1322,7 @@
     <t>TC158 Molina Clear Cost Turquoise 3 EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Turquoise 3 EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Clear Cost Turquoise 3 EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_G13_90.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_G13_90.pdf</t>
@@ -1331,7 +1331,7 @@
     <t>TC159 Molina Clear Cost Silver On Exchange NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Silver On Exchange</t>
+    <t>Schedule of Benefits – Molina Clear Cost Silver On Exchange</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_1.pdf</t>
@@ -1340,7 +1340,7 @@
     <t>TC160 Molina Native American Clear Cost Silver Zero NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Clear Cost Silver Zero</t>
+    <t>Schedule of Benefits – Molina Native American Clear Cost Silver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_2.pdf</t>
@@ -1349,7 +1349,7 @@
     <t>TC161 Molina Native American Clear Cost Silver LCS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Clear Cost Silver LCS</t>
+    <t>Schedule of Benefits – Molina Native American Clear Cost Silver LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_3.pdf</t>
@@ -1358,7 +1358,7 @@
     <t>TC162 Molina Clear Cost Silver 73 NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Silver 73</t>
+    <t>Schedule of Benefits – Molina Clear Cost Silver 73</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_4.pdf</t>
@@ -1367,7 +1367,7 @@
     <t>TC163 Molina Clear Cost Silver 87 NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Silver 87</t>
+    <t>Schedule of Benefits – Molina Clear Cost Silver 87</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_9.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_9.pdf</t>
@@ -1376,7 +1376,7 @@
     <t>TC164 Molina Clear Cost Silver 94 NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Silver 94</t>
+    <t>Schedule of Benefits – Molina Clear Cost Silver 94</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S13_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S13_5.pdf</t>
@@ -1385,7 +1385,7 @@
     <t>TC165 Molina Clear Cost Turquoise 2 with EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Turquoise 2 with EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Clear Cost Turquoise 2 with EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM26SOBE_S13_95.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM26SOBS_S13_95.pdf</t>
@@ -1394,7 +1394,7 @@
     <t>TC166 Molina Clear Cost Turquoise 1 with EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Clear Cost Turquoise 1 with EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Clear Cost Turquoise 1 with EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM26SOBE_S13_99.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM26SOBS_S13_99.pdf</t>
@@ -1403,7 +1403,7 @@
     <t>TC167 Molina Silver Saver On Exchange NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver On Exchange</t>
+    <t>Schedule of Benefits – Molina Silver Saver On Exchange</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_1.pdf</t>
@@ -1412,7 +1412,7 @@
     <t>TC168 Molina Native American Silver Saver Zero NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Silver Saver Zero</t>
+    <t>Schedule of Benefits – Molina Native American Silver Saver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_2.pdf</t>
@@ -1421,7 +1421,7 @@
     <t>TC169 Molina Native American Silver Saver LCS NM-2027</t>
   </si>
   <si>
-    <t>Molina Native American Silver Saver LCS</t>
+    <t>Schedule of Benefits – Molina Native American Silver Saver LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_3.pdf</t>
@@ -1430,7 +1430,7 @@
     <t>TC170 Molina Silver Saver 73 NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 73</t>
+    <t>Schedule of Benefits – Molina Silver Saver 73</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_4.pdf</t>
@@ -1439,7 +1439,7 @@
     <t>TC171 Molina Silver Saver 87 NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 87</t>
+    <t>Schedule of Benefits – Molina Silver Saver 87</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_9.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_9.pdf</t>
@@ -1448,7 +1448,7 @@
     <t>TC172 Molina Silver Saver 94 NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver 94</t>
+    <t>Schedule of Benefits – Molina Silver Saver 94</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_S14_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_S14_5.pdf</t>
@@ -1457,7 +1457,7 @@
     <t>TC173 Molina Silver Saver Turquoise 2 with EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver Turquoise 2 with EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Silver Saver Turquoise 2 with EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM26SOBE_S14_95.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM26SOBS_S14_95.pdf</t>
@@ -1466,7 +1466,7 @@
     <t>TC174 Molina Silver Saver Turquoise 1 with EXTRA SAVINGS NM-2027</t>
   </si>
   <si>
-    <t>Molina Silver Saver Turquoise 1 with EXTRA SAVINGS</t>
+    <t>Schedule of Benefits – Molina Silver Saver Turquoise 1 with EXTRA SAVINGS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM26SOBE_S14_99.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM26SOBS_S14_99.pdf</t>
@@ -1475,7 +1475,7 @@
     <t>TC175 Molina Bronze Saver 7000 On Exchange NM-2027</t>
   </si>
   <si>
-    <t>Molina Bronze Saver 7000 On Exchange</t>
+    <t>Schedule of Benefits – Molina Bronze Saver 7000 On Exchange</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/english/NM27SOBE_B12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nm/materials/SOB/2027/spanish/NM27SOBS_B12_1.pdf</t>
@@ -1499,7 +1499,7 @@
     <t>IL</t>
   </si>
   <si>
-    <t>Molina Open Gold Enhanced 750</t>
+    <t>Schedule of Benefits – Molina Open Gold Enhanced 750</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G12_1.pdf</t>
@@ -1508,7 +1508,7 @@
     <t>TC179 Molina Open Gold Enhanced Zero IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Enhanced Zero</t>
+    <t>Schedule of Benefits – Molina Open Gold Enhanced Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G12_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G12_2.pdf</t>
@@ -1517,7 +1517,7 @@
     <t>TC180 Molina Open Gold Enhanced 750 LCS IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Enhanced 750 LCS</t>
+    <t>Schedule of Benefits – Molina Open Gold Enhanced 750 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G12_3.pdf</t>
@@ -1526,7 +1526,7 @@
     <t>TC181 Molina Open Silver Empower 2750 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Empower 2750</t>
+    <t>Schedule of Benefits – Molina Open Silver Empower 2750</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S16_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_S16_0.pdf</t>
@@ -1535,7 +1535,7 @@
     <t>TC182 Molina Open Silver Empower 4500 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Empower 4500</t>
+    <t>Schedule of Benefits – Molina Open Silver Empower 4500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S18_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_S18_0.pdf</t>
@@ -1544,7 +1544,7 @@
     <t>TC183 Molina Open Silver Empower 5500 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Empower 5500</t>
+    <t>Schedule of Benefits – Molina Open Silver Empower 5500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S19_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_S19_0.pdf</t>
@@ -1553,7 +1553,7 @@
     <t>TC184 Molina Open Gold Empower 2000 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Empower 2000</t>
+    <t>Schedule of Benefits – Molina Open Gold Empower 2000</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G16_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_G16_0.pdf</t>
@@ -1562,7 +1562,7 @@
     <t>TC185 Molina Open Gold Empower 2000 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Empower 2000 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Empower 2000 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G16V_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_G16V_0.pdf</t>
@@ -1571,7 +1571,7 @@
     <t>TC186 Molina Open Silver Empower 3750 Plus with Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Empower 3750 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Empower 3750 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S17DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_S17DV_0.pdf</t>
@@ -1580,7 +1580,7 @@
     <t>TC187 Molina Open Gold Empower 2000 Plus with Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Empower 2000 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Empower 2000 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBS_G16DV_0.pdf</t>
@@ -1589,7 +1589,7 @@
     <t>TC188 Molina Open Gold Core 1500 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1_1.pdf</t>
@@ -1598,7 +1598,7 @@
     <t>TC189 Molina Open Gold Core Zero IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core Zero</t>
+    <t>Schedule of Benefits – Molina Open Gold Core Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1_2.pdf</t>
@@ -1607,7 +1607,7 @@
     <t>TC190 Molina Open Gold Core 1500 LCS IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500 LCS</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1_3.pdf</t>
@@ -1616,7 +1616,7 @@
     <t>TC191 Molina Open Silver Core 70 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 70</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 70</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_1.pdf</t>
@@ -1625,7 +1625,7 @@
     <t>TC192 Molina Open Silver Core Zero IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core Zero</t>
+    <t>Schedule of Benefits – Molina Open Silver Core Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_2.pdf</t>
@@ -1634,7 +1634,7 @@
     <t>TC193 Molina Open Silver Core 70 LCS IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 70 LCS</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 70 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_3.pdf</t>
@@ -1643,7 +1643,7 @@
     <t>TC194 Molina Open Silver Core 73 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 73</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 73</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_4.pdf</t>
@@ -1652,7 +1652,7 @@
     <t>TC195 Molina Open Silver Core 87 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 87</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 87</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_5.pdf</t>
@@ -1661,7 +1661,7 @@
     <t>TC196 Molina Open Silver Core 94 IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 94</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 94</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1_6.pdf</t>
@@ -1670,7 +1670,7 @@
     <t>TC197 Molina Open Silver Saver 70 with Four Free PCP or MH Visits IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver 70 with Four Free PCP or MH Visits</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver 70 with Four Free PCP or MH Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_1.pdf</t>
@@ -1679,7 +1679,7 @@
     <t>TC198 Molina Open Silver Saver Zero IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver Zero</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver Zero</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_2.pdf</t>
@@ -1688,7 +1688,7 @@
     <t>TC199 Molina Open Silver Saver  LCS with Four Free PCP or MH Visits IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver  LCS with Four Free PCP or MH Visits</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver  LCS with Four Free PCP or MH Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_3.pdf</t>
@@ -1697,7 +1697,7 @@
     <t>TC200 Molina Open Silver Saver 73 with Four Free PCP or MH Visits IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver 73 with Four Free PCP or MH Visits</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver 73 with Four Free PCP or MH Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_4.pdf</t>
@@ -1706,7 +1706,7 @@
     <t>TC201 Molina Open Silver Saver 87 with Four Free PCP or MH Visits IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver 87 with Four Free PCP or MH Visits</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver 87 with Four Free PCP or MH Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_5.pdf</t>
@@ -1715,7 +1715,7 @@
     <t>TC202 Molina Open Silver Saver 94 with Four Free PCP or MH Visits IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Saver 94 with Four Free PCP or MH Visits</t>
+    <t>Schedule of Benefits – Molina Open Silver Saver 94 with Four Free PCP or MH Visits</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S12_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S12_6.pdf</t>
@@ -1724,7 +1724,7 @@
     <t>TC203 Molina Open Gold Core 1500 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1V_1.pdf</t>
@@ -1733,7 +1733,7 @@
     <t>TC204 Molina Open Gold Core Zero Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1V_2.pdf</t>
@@ -1742,7 +1742,7 @@
     <t>TC205 Molina Open Gold Core 1500 LCS Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1V_3.pdf</t>
@@ -1751,7 +1751,7 @@
     <t>TC206 Molina Open Silver Core 70 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 70 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 70 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_1.pdf</t>
@@ -1760,7 +1760,7 @@
     <t>TC207 Molina Open Silver Core Zero Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_2.pdf</t>
@@ -1769,7 +1769,7 @@
     <t>TC208 Molina Open Silver Core 70 LCS Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 70 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 70 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_3.pdf</t>
@@ -1778,7 +1778,7 @@
     <t>TC209 Molina Open Silver Core 73 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 73 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 73 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_4.pdf</t>
@@ -1787,7 +1787,7 @@
     <t>TC210 Molina Open Silver Core 87 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 87 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 87 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_5.pdf</t>
@@ -1796,7 +1796,7 @@
     <t>TC211 Molina Open Silver Core 94 Plus with Adult Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 94 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 94 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1V_6.pdf</t>
@@ -1805,7 +1805,7 @@
     <t>TC212 Molina Open Gold Core 1500 Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500 Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500 Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1DV_1.pdf</t>
@@ -1814,7 +1814,7 @@
     <t>TC213 Molina Open Gold Core Zero Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core Zero Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core Zero Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1DV_2.pdf</t>
@@ -1823,7 +1823,7 @@
     <t>TC214 Molina Open Gold Core 1500 LCS Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Gold Core 1500 LCS Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Gold Core 1500 LCS Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1DV_3.pdf</t>
@@ -1832,7 +1832,7 @@
     <t>TC215 Molina Open Silver Core 70 Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 70 Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 70 Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1DV_1.pdf</t>
@@ -1841,7 +1841,7 @@
     <t>TC216 Molina Open Silver Core Zero Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core Zero Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core Zero Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1DV_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1DV_2.pdf</t>
@@ -1856,7 +1856,7 @@
     <t>TC218 Molina Open Silver Core 73 Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 73 Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 73 Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1DV_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1DV_4.pdf</t>
@@ -1865,7 +1865,7 @@
     <t>TC219 Molina Open Silver Core 87 Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 87 Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 87 Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1DV_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1DV_5.pdf</t>
@@ -1874,7 +1874,7 @@
     <t>TC220 Molina Open Silver Core 94 Plus with Rx Copay and Adult Dental and Vision IL-2027</t>
   </si>
   <si>
-    <t>Molina Open Silver Core 94 Plus with Rx Copay and Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Open Silver Core 94 Plus with Rx Copay and Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_S1DV_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_S1DV_6.pdf</t>
@@ -2030,7 +2030,7 @@
     <t>TC245 Molina Gold Enhanced 750 Plus with Adult Dental and Vision MI-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 750 Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 750 Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/english/MI27SOBE_G12DV_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/spanish/MI27SOBS_G12DV_1.pdf</t>
@@ -2045,7 +2045,7 @@
     <t>TC247 Molina Gold Enhanced 750 LCS Plus with Adult Dental and Vision MI-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 750 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 750 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/english/MI27SOBE_G12DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/spanish/MI27SOBS_G12DV_3.pdf</t>
@@ -2057,7 +2057,7 @@
     <t>TX</t>
   </si>
   <si>
-    <t>Silver 3</t>
+    <t>Schedule of Benefits – Silver 3</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_S3_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_S3_0.pdf</t>
@@ -2156,7 +2156,7 @@
     <t>TC264 Molina Gold Enhanced 750 TX-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 750</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 750</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G12_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G12_1.pdf</t>
@@ -2171,7 +2171,7 @@
     <t>TC266 Molina Gold Enhanced 750 LCS TX-2027</t>
   </si>
   <si>
-    <t>Molina Gold Enhanced 750 LCS</t>
+    <t>Schedule of Benefits – Molina Gold Enhanced 750 LCS</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G12_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G12_3.pdf</t>
@@ -2264,7 +2264,7 @@
     <t>TC281 Molina Gold Saver 750 Plus with Adult Vision TX-2027</t>
   </si>
   <si>
-    <t>Molina Gold Saver 750 Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Saver 750 Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G12V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G12V_1.pdf</t>
@@ -2273,7 +2273,7 @@
     <t>TC282 Molina Gold Saver Zero Plus with Adult Vision TX-2027</t>
   </si>
   <si>
-    <t>Molina Gold Saver Zero Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Saver Zero Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G12V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G12V_2.pdf</t>
@@ -2282,7 +2282,7 @@
     <t>TC283 Molina Gold Saver 750 LCS Plus with Adult Vision TX-2027</t>
   </si>
   <si>
-    <t>Molina Gold Saver 750 LCS Plus with Adult Vision</t>
+    <t>Schedule of Benefits – Molina Gold Saver 750 LCS Plus with Adult Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G12V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G12V_3.pdf</t>
@@ -2351,7 +2351,7 @@
     <t>TC294 Molina Silver Core 70 LCS Plus with Adult Dental and Vision TX-2027</t>
   </si>
   <si>
-    <t>Molina Silver Core 70 LCS Plus with Adult Dental and Vision</t>
+    <t>Schedule of Benefits – Molina Silver Core 70 LCS Plus with Adult Dental and Vision</t>
   </si>
   <si>
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_S1DV_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_S1DV_3.pdf</t>
@@ -2423,82 +2423,82 @@
     <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/english/TX27SOBE_G16DV_0.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/tx/materials/SOB/2027/spanish/TX27SOBS_G16DV_0.pdf</t>
   </si>
   <si>
+    <t>TC306 Molina Gold Core 1500 Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC307 Molina Gold Core Zero Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC308 Molina Gold Core 1500 LCS Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC309 Molina Silver Core 70 Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_1.pdf</t>
+  </si>
+  <si>
+    <t>TC310 Molina Silver Core Zero Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_2.pdf</t>
+  </si>
+  <si>
+    <t>TC311 Molina Silver Core LCS Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_3.pdf</t>
+  </si>
+  <si>
+    <t>TC312 Molina Silver Core 73 Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_4.pdf</t>
+  </si>
+  <si>
+    <t>TC313 Molina Silver Core 87 Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_5.pdf</t>
+  </si>
+  <si>
+    <t>TC314 Molina Silver Core 94 Plus with Adult Vision NV-2027</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_6.pdf</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>AppUrl</t>
+  </si>
+  <si>
+    <t>https://uat-pws.molinahealthcare.com/</t>
+  </si>
+  <si>
+    <t>Landing URL for the Plan Search suite. Change to point at Q1/Q2/Q3/UAT/prod without editing code. Precedence: MARKETPLACE_PLANS_URL env var &gt; this Value &gt; framework.config.js default.</t>
+  </si>
+  <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>TC306 Molina Gold Core 1500 Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>NV</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_1.pdf</t>
-  </si>
-  <si>
-    <t>TC307 Molina Gold Core Zero Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_2.pdf</t>
-  </si>
-  <si>
-    <t>TC308 Molina Gold Core 1500 LCS Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_G1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_G1V_3.pdf</t>
-  </si>
-  <si>
-    <t>TC309 Molina Silver Core 70 Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_1.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_1.pdf</t>
-  </si>
-  <si>
-    <t>TC310 Molina Silver Core Zero Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_2.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_2.pdf</t>
-  </si>
-  <si>
-    <t>TC311 Molina Silver Core LCS Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_3.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_3.pdf</t>
-  </si>
-  <si>
-    <t>TC312 Molina Silver Core 73 Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_4.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_4.pdf</t>
-  </si>
-  <si>
-    <t>TC313 Molina Silver Core 87 Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_5.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_5.pdf</t>
-  </si>
-  <si>
-    <t>TC314 Molina Silver Core 94 Plus with Adult Vision NV-2027</t>
-  </si>
-  <si>
-    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/english/NV27SOBE_S1V_6.pdf|https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/nv/materials/SOB/2027/spanish/NV27SOBS_S1V_6.pdf</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>AppUrl</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/</t>
-  </si>
-  <si>
-    <t>Landing URL for the Plan Search suite. Change to point at Q1/Q2/Q3/UAT/prod without editing code. Precedence: MARKETPLACE_PLANS_URL env var &gt; this Value &gt; framework.config.js default.</t>
   </si>
 </sst>
 </file>
@@ -2599,10 +2599,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2634,10 +2634,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2879,10 +2879,10 @@
   <dimension ref="A1:I315"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="70.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="241.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.296875" customWidth="1"/>
+    <col min="7" max="7" width="18.09765625" customWidth="1"/>
+    <col min="8" max="8" width="70.3984375" customWidth="1"/>
+    <col min="9" max="9" width="241.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -5437,9 +5437,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B89" t="s">
         <v>261</v>
@@ -5466,9 +5466,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B90" t="s">
         <v>264</v>
@@ -5495,9 +5495,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B91" t="s">
         <v>266</v>
@@ -5524,9 +5524,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B92" t="s">
         <v>268</v>
@@ -5553,9 +5553,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B93" t="s">
         <v>270</v>
@@ -5582,9 +5582,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B94" t="s">
         <v>272</v>
@@ -5611,9 +5611,9 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B95" t="s">
         <v>274</v>
@@ -5640,9 +5640,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B96" t="s">
         <v>276</v>
@@ -5669,9 +5669,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B97" t="s">
         <v>278</v>
@@ -5698,9 +5698,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B98" t="s">
         <v>280</v>
@@ -5727,9 +5727,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B99" t="s">
         <v>282</v>
@@ -5756,9 +5756,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B100" t="s">
         <v>284</v>
@@ -5785,9 +5785,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B101" t="s">
         <v>286</v>
@@ -5814,9 +5814,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B102" t="s">
         <v>288</v>
@@ -5843,9 +5843,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B103" t="s">
         <v>290</v>
@@ -5872,9 +5872,9 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B104" t="s">
         <v>292</v>
@@ -5901,9 +5901,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B105" t="s">
         <v>294</v>
@@ -5930,9 +5930,9 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B106" t="s">
         <v>296</v>
@@ -5959,9 +5959,9 @@
         <v>297</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B107" t="s">
         <v>298</v>
@@ -5988,9 +5988,9 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B108" t="s">
         <v>300</v>
@@ -6017,9 +6017,9 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B109" t="s">
         <v>302</v>
@@ -6046,9 +6046,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B110" t="s">
         <v>304</v>
@@ -6075,9 +6075,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B111" t="s">
         <v>306</v>
@@ -6104,9 +6104,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B112" t="s">
         <v>308</v>
@@ -6133,9 +6133,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B113" t="s">
         <v>310</v>
@@ -6162,9 +6162,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B114" t="s">
         <v>312</v>
@@ -6191,9 +6191,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B115" t="s">
         <v>314</v>
@@ -6220,9 +6220,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B116" t="s">
         <v>316</v>
@@ -6249,9 +6249,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B117" t="s">
         <v>318</v>
@@ -6278,9 +6278,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B118" t="s">
         <v>320</v>
@@ -6307,9 +6307,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B119" t="s">
         <v>322</v>
@@ -6336,9 +6336,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B120" t="s">
         <v>324</v>
@@ -6365,9 +6365,9 @@
         <v>325</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>824</v>
       </c>
       <c r="B121" t="s">
         <v>326</v>
@@ -11759,15 +11759,15 @@
         <v>798</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>9</v>
       </c>
       <c r="B307" t="s">
+        <v>799</v>
+      </c>
+      <c r="C307" t="s">
         <v>800</v>
-      </c>
-      <c r="C307" t="s">
-        <v>801</v>
       </c>
       <c r="D307" t="s">
         <v>12</v>
@@ -11785,18 +11785,18 @@
         <v>106</v>
       </c>
       <c r="I307" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>9</v>
+      </c>
+      <c r="B308" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>9</v>
-      </c>
-      <c r="B308" t="s">
-        <v>803</v>
-      </c>
       <c r="C308" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D308" t="s">
         <v>12</v>
@@ -11814,18 +11814,18 @@
         <v>109</v>
       </c>
       <c r="I308" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>9</v>
-      </c>
-      <c r="B309" t="s">
-        <v>805</v>
-      </c>
       <c r="C309" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D309" t="s">
         <v>12</v>
@@ -11843,18 +11843,18 @@
         <v>112</v>
       </c>
       <c r="I309" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>9</v>
-      </c>
-      <c r="B310" t="s">
-        <v>807</v>
-      </c>
       <c r="C310" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D310" t="s">
         <v>12</v>
@@ -11872,18 +11872,18 @@
         <v>115</v>
       </c>
       <c r="I310" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>9</v>
-      </c>
-      <c r="B311" t="s">
-        <v>809</v>
-      </c>
       <c r="C311" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D311" t="s">
         <v>12</v>
@@ -11901,18 +11901,18 @@
         <v>118</v>
       </c>
       <c r="I311" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
-        <v>799</v>
-      </c>
-      <c r="B312" t="s">
-        <v>811</v>
-      </c>
       <c r="C312" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D312" t="s">
         <v>12</v>
@@ -11930,18 +11930,18 @@
         <v>121</v>
       </c>
       <c r="I312" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
-        <v>799</v>
-      </c>
-      <c r="B313" t="s">
-        <v>813</v>
-      </c>
       <c r="C313" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D313" t="s">
         <v>12</v>
@@ -11959,18 +11959,18 @@
         <v>124</v>
       </c>
       <c r="I313" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
-        <v>9</v>
-      </c>
-      <c r="B314" t="s">
-        <v>815</v>
-      </c>
       <c r="C314" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D314" t="s">
         <v>12</v>
@@ -11988,18 +11988,18 @@
         <v>127</v>
       </c>
       <c r="I314" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
-        <v>9</v>
-      </c>
-      <c r="B315" t="s">
-        <v>817</v>
-      </c>
       <c r="C315" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D315" t="s">
         <v>12</v>
@@ -12017,20 +12017,20 @@
         <v>130</v>
       </c>
       <c r="I315" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I315" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="NV"/>
+        <filter val="ID"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I306 A312:I313 B307:I307 B308:I311 B315:I315 B314:I314" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I2 B116:I315 B115:I115 B3:I114" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12047,24 +12047,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B1" t="s">
         <v>819</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>820</v>
-      </c>
-      <c r="C1" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2" t="s">
         <v>822</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>823</v>
-      </c>
-      <c r="C2" t="s">
-        <v>824</v>
       </c>
     </row>
   </sheetData>

--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/seeram_tarunvardhan_molinahealthcare_com/Documents/Desktop/Automationss/IMP/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_95EE763EA5C74F31F8D301139C6A6534037FAE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEBF3BD4-DC8A-4B8D-9104-26C8A6DFC4FB}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_95EE763EA5C74F31F8D301139C6A6534037FAE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1AF6170-09A8-4D04-BA17-59C4384E566F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plans" sheetId="1" r:id="rId1"/>
@@ -2741,9 +2741,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3086,13 +3089,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I337"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="8" max="8" width="106.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="179.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="106.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="179.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3121,7 +3124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3179,7 +3182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3237,7 +3240,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3266,7 +3269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3295,7 +3298,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3324,7 +3327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3411,7 +3414,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3440,7 +3443,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3469,7 +3472,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -3498,7 +3501,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3527,7 +3530,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -3556,7 +3559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -3585,7 +3588,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -3614,7 +3617,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -3643,7 +3646,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -3672,7 +3675,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -3701,7 +3704,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -3730,7 +3733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -3759,7 +3762,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -3788,7 +3791,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -3817,7 +3820,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3875,7 +3878,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -3904,7 +3907,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -3933,7 +3936,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3991,7 +3994,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -4020,7 +4023,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -4049,7 +4052,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -4078,7 +4081,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4223,7 +4226,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4252,7 +4255,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -4281,7 +4284,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -4339,7 +4342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -4397,7 +4400,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -4426,7 +4429,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -4455,7 +4458,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -4484,7 +4487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -4513,7 +4516,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -4542,7 +4545,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -4571,7 +4574,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -4600,7 +4603,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -4629,7 +4632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -4658,7 +4661,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -4687,7 +4690,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -4716,7 +4719,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -4745,7 +4748,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -4803,7 +4806,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -4832,7 +4835,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -4890,7 +4893,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4919,7 +4922,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -4977,7 +4980,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -5035,7 +5038,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -5064,7 +5067,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -5093,7 +5096,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -5122,7 +5125,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -5151,7 +5154,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -5180,7 +5183,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -5209,7 +5212,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -5267,7 +5270,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -5296,7 +5299,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -5325,7 +5328,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -5354,7 +5357,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -5383,7 +5386,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -5412,7 +5415,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -5441,7 +5444,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -5470,7 +5473,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -5499,7 +5502,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -5557,7 +5560,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -5586,7 +5589,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -5615,7 +5618,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -5644,9 +5647,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B89" t="s">
         <v>261</v>
@@ -5673,9 +5676,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B90" t="s">
         <v>264</v>
@@ -5702,9 +5705,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B91" t="s">
         <v>266</v>
@@ -5731,9 +5734,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B92" t="s">
         <v>268</v>
@@ -5760,7 +5763,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -5789,7 +5792,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -5818,7 +5821,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -5847,7 +5850,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -5876,9 +5879,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B97" t="s">
         <v>278</v>
@@ -5905,9 +5908,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B98" t="s">
         <v>280</v>
@@ -5934,9 +5937,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s">
         <v>282</v>
@@ -5963,9 +5966,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B100" t="s">
         <v>284</v>
@@ -5992,7 +5995,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -6021,7 +6024,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -6050,7 +6053,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -6079,7 +6082,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -6108,9 +6111,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B105" t="s">
         <v>294</v>
@@ -6137,9 +6140,9 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B106" t="s">
         <v>296</v>
@@ -6166,9 +6169,9 @@
         <v>297</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
         <v>298</v>
@@ -6195,9 +6198,9 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
         <v>300</v>
@@ -6224,7 +6227,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -6253,7 +6256,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -6311,7 +6314,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -6340,9 +6343,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B113" t="s">
         <v>310</v>
@@ -6369,9 +6372,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B114" t="s">
         <v>312</v>
@@ -6398,9 +6401,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B115" t="s">
         <v>314</v>
@@ -6427,9 +6430,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B116" t="s">
         <v>316</v>
@@ -6456,7 +6459,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -6485,7 +6488,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -6514,7 +6517,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -6543,7 +6546,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -6572,7 +6575,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -6601,7 +6604,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -6659,7 +6662,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -6717,7 +6720,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -6746,7 +6749,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -6775,7 +6778,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -6804,7 +6807,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -6833,7 +6836,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -6862,7 +6865,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -6920,7 +6923,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -6949,7 +6952,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -6978,7 +6981,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -7007,7 +7010,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -7036,7 +7039,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -7065,7 +7068,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -7094,7 +7097,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -7123,7 +7126,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -7152,7 +7155,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -7181,7 +7184,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -7239,7 +7242,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -7268,7 +7271,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -7297,7 +7300,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -7326,7 +7329,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -7355,9 +7358,9 @@
         <v>397</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B148" t="s">
         <v>398</v>
@@ -7384,9 +7387,9 @@
         <v>401</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B149" t="s">
         <v>402</v>
@@ -7413,9 +7416,9 @@
         <v>404</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B150" t="s">
         <v>405</v>
@@ -7442,9 +7445,9 @@
         <v>407</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B151" t="s">
         <v>408</v>
@@ -7471,7 +7474,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -7500,7 +7503,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -7529,7 +7532,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -7558,7 +7561,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -7587,7 +7590,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -7616,7 +7619,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -7645,7 +7648,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -7674,9 +7677,9 @@
         <v>431</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B159" t="s">
         <v>432</v>
@@ -7703,9 +7706,9 @@
         <v>434</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B160" t="s">
         <v>435</v>
@@ -7732,9 +7735,9 @@
         <v>437</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B161" t="s">
         <v>438</v>
@@ -7761,9 +7764,9 @@
         <v>440</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B162" t="s">
         <v>441</v>
@@ -7790,7 +7793,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -7819,7 +7822,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>9</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -7877,7 +7880,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -7906,7 +7909,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -7935,7 +7938,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>9</v>
       </c>
@@ -7964,7 +7967,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>9</v>
       </c>
@@ -7993,7 +7996,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>9</v>
       </c>
@@ -8022,7 +8025,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -8051,7 +8054,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -8080,7 +8083,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>9</v>
       </c>
@@ -8109,7 +8112,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>9</v>
       </c>
@@ -8138,7 +8141,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -8167,7 +8170,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -8196,7 +8199,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -8225,7 +8228,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -8254,7 +8257,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>9</v>
       </c>
@@ -8283,7 +8286,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -8312,7 +8315,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -8341,7 +8344,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -8370,7 +8373,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -8399,7 +8402,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -8428,7 +8431,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -8457,7 +8460,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -8486,7 +8489,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -8515,7 +8518,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>9</v>
       </c>
@@ -8544,7 +8547,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -8573,7 +8576,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -8602,7 +8605,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -8631,7 +8634,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -8660,7 +8663,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -8689,7 +8692,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -8718,7 +8721,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -8747,7 +8750,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -8776,7 +8779,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -8805,7 +8808,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -8834,7 +8837,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>9</v>
       </c>
@@ -8863,7 +8866,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>9</v>
       </c>
@@ -8892,7 +8895,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -8921,7 +8924,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -8950,7 +8953,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -8979,7 +8982,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -9008,7 +9011,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -9037,7 +9040,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -9066,7 +9069,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -9095,7 +9098,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -9124,7 +9127,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -9153,7 +9156,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -9182,7 +9185,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -9211,7 +9214,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -9240,7 +9243,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -9269,7 +9272,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -9298,7 +9301,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -9327,7 +9330,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -9356,7 +9359,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -9385,7 +9388,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -9414,7 +9417,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -9443,7 +9446,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -9472,7 +9475,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -9501,7 +9504,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -9530,7 +9533,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -9559,7 +9562,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -9588,7 +9591,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -9617,7 +9620,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -9646,7 +9649,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>9</v>
       </c>
@@ -9675,7 +9678,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>9</v>
       </c>
@@ -9704,7 +9707,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -9733,7 +9736,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>9</v>
       </c>
@@ -9762,7 +9765,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>9</v>
       </c>
@@ -9791,7 +9794,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -9820,7 +9823,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>9</v>
       </c>
@@ -9849,7 +9852,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -9878,7 +9881,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>9</v>
       </c>
@@ -9907,7 +9910,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>9</v>
       </c>
@@ -9936,7 +9939,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>9</v>
       </c>
@@ -9965,7 +9968,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>9</v>
       </c>
@@ -9994,7 +9997,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>9</v>
       </c>
@@ -10023,7 +10026,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>9</v>
       </c>
@@ -10052,7 +10055,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>9</v>
       </c>
@@ -10081,7 +10084,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>9</v>
       </c>
@@ -10110,7 +10113,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -10139,7 +10142,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>9</v>
       </c>
@@ -10168,7 +10171,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>9</v>
       </c>
@@ -10197,7 +10200,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -10226,7 +10229,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>9</v>
       </c>
@@ -10255,7 +10258,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>9</v>
       </c>
@@ -10284,7 +10287,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>9</v>
       </c>
@@ -10313,7 +10316,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>9</v>
       </c>
@@ -10342,7 +10345,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>9</v>
       </c>
@@ -10371,7 +10374,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -10400,7 +10403,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>9</v>
       </c>
@@ -10429,7 +10432,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>9</v>
       </c>
@@ -10458,7 +10461,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>9</v>
       </c>
@@ -10487,7 +10490,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>9</v>
       </c>
@@ -10516,7 +10519,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>9</v>
       </c>
@@ -10545,7 +10548,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>9</v>
       </c>
@@ -10574,7 +10577,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>9</v>
       </c>
@@ -10603,7 +10606,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>9</v>
       </c>
@@ -10632,7 +10635,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -10661,7 +10664,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>356</v>
       </c>
@@ -10690,7 +10693,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>356</v>
       </c>
@@ -10719,7 +10722,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>356</v>
       </c>
@@ -10748,7 +10751,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>356</v>
       </c>
@@ -10777,9 +10780,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B266" t="s">
         <v>726</v>
@@ -10806,9 +10809,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B267" t="s">
         <v>728</v>
@@ -10835,9 +10838,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B268" t="s">
         <v>730</v>
@@ -10864,9 +10867,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B269" t="s">
         <v>732</v>
@@ -10893,7 +10896,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>356</v>
       </c>
@@ -10922,7 +10925,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>356</v>
       </c>
@@ -10951,7 +10954,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>356</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>356</v>
       </c>
@@ -11009,9 +11012,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B274" t="s">
         <v>742</v>
@@ -11038,9 +11041,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B275" t="s">
         <v>744</v>
@@ -11067,9 +11070,9 @@
         <v>745</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B276" t="s">
         <v>746</v>
@@ -11096,9 +11099,9 @@
         <v>747</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B277" t="s">
         <v>748</v>
@@ -11125,9 +11128,9 @@
         <v>749</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B278" t="s">
         <v>750</v>
@@ -11154,7 +11157,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>356</v>
       </c>
@@ -11183,7 +11186,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>356</v>
       </c>
@@ -11212,7 +11215,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>356</v>
       </c>
@@ -11241,7 +11244,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>356</v>
       </c>
@@ -11270,9 +11273,9 @@
         <v>761</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B283" t="s">
         <v>762</v>
@@ -11299,9 +11302,9 @@
         <v>763</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B284" t="s">
         <v>764</v>
@@ -11328,9 +11331,9 @@
         <v>765</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B285" t="s">
         <v>766</v>
@@ -11357,9 +11360,9 @@
         <v>767</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B286" t="s">
         <v>768</v>
@@ -11386,9 +11389,9 @@
         <v>769</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B287" t="s">
         <v>770</v>
@@ -11415,9 +11418,9 @@
         <v>771</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B288" t="s">
         <v>772</v>
@@ -11444,7 +11447,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>356</v>
       </c>
@@ -11473,7 +11476,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>356</v>
       </c>
@@ -11502,7 +11505,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>356</v>
       </c>
@@ -11531,7 +11534,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>356</v>
       </c>
@@ -11560,9 +11563,9 @@
         <v>781</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B293" t="s">
         <v>782</v>
@@ -11589,9 +11592,9 @@
         <v>783</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B294" t="s">
         <v>784</v>
@@ -11618,9 +11621,9 @@
         <v>785</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B295" t="s">
         <v>786</v>
@@ -11647,9 +11650,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B296" t="s">
         <v>788</v>
@@ -11676,9 +11679,9 @@
         <v>789</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B297" t="s">
         <v>790</v>
@@ -11705,9 +11708,9 @@
         <v>791</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B298" t="s">
         <v>792</v>
@@ -11734,9 +11737,9 @@
         <v>793</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B299" t="s">
         <v>794</v>
@@ -11763,9 +11766,9 @@
         <v>795</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B300" t="s">
         <v>796</v>
@@ -11792,9 +11795,9 @@
         <v>797</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B301" t="s">
         <v>798</v>
@@ -11821,9 +11824,9 @@
         <v>799</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B302" t="s">
         <v>800</v>
@@ -11850,9 +11853,9 @@
         <v>801</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B303" t="s">
         <v>802</v>
@@ -11879,9 +11882,9 @@
         <v>803</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B304" t="s">
         <v>804</v>
@@ -11908,9 +11911,9 @@
         <v>805</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B305" t="s">
         <v>806</v>
@@ -11937,9 +11940,9 @@
         <v>808</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B306" t="s">
         <v>809</v>
@@ -11966,9 +11969,9 @@
         <v>810</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B307" t="s">
         <v>811</v>
@@ -11995,9 +11998,9 @@
         <v>812</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B308" t="s">
         <v>813</v>
@@ -12024,9 +12027,9 @@
         <v>814</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B309" t="s">
         <v>815</v>
@@ -12053,9 +12056,9 @@
         <v>816</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B310" t="s">
         <v>817</v>
@@ -12082,9 +12085,9 @@
         <v>818</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B311" t="s">
         <v>819</v>
@@ -12111,9 +12114,9 @@
         <v>820</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B312" t="s">
         <v>821</v>
@@ -12140,9 +12143,9 @@
         <v>822</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B313" t="s">
         <v>823</v>
@@ -12169,9 +12172,9 @@
         <v>824</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B314" t="s">
         <v>825</v>
@@ -12198,9 +12201,9 @@
         <v>826</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B315" t="s">
         <v>827</v>
@@ -12227,9 +12230,9 @@
         <v>828</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B316" t="s">
         <v>829</v>
@@ -12256,9 +12259,9 @@
         <v>830</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B317" t="s">
         <v>831</v>
@@ -12266,7 +12269,7 @@
       <c r="C317" t="s">
         <v>717</v>
       </c>
-      <c r="D317">
+      <c r="D317" s="2">
         <v>2027</v>
       </c>
       <c r="E317" t="s">
@@ -12285,9 +12288,9 @@
         <v>833</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B318" t="s">
         <v>834</v>
@@ -12295,7 +12298,7 @@
       <c r="C318" t="s">
         <v>717</v>
       </c>
-      <c r="D318">
+      <c r="D318" s="2">
         <v>2027</v>
       </c>
       <c r="E318" t="s">
@@ -12314,9 +12317,9 @@
         <v>836</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B319" t="s">
         <v>837</v>
@@ -12324,7 +12327,7 @@
       <c r="C319" t="s">
         <v>717</v>
       </c>
-      <c r="D319">
+      <c r="D319" s="2">
         <v>2027</v>
       </c>
       <c r="E319" t="s">
@@ -12343,9 +12346,9 @@
         <v>839</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B320" t="s">
         <v>840</v>
@@ -12353,7 +12356,7 @@
       <c r="C320" t="s">
         <v>717</v>
       </c>
-      <c r="D320">
+      <c r="D320" s="2">
         <v>2027</v>
       </c>
       <c r="E320" t="s">
@@ -12372,9 +12375,9 @@
         <v>842</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B321" t="s">
         <v>843</v>
@@ -12382,7 +12385,7 @@
       <c r="C321" t="s">
         <v>717</v>
       </c>
-      <c r="D321">
+      <c r="D321" s="2">
         <v>2027</v>
       </c>
       <c r="E321" t="s">
@@ -12401,9 +12404,9 @@
         <v>845</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B322" t="s">
         <v>846</v>
@@ -12411,7 +12414,7 @@
       <c r="C322" t="s">
         <v>717</v>
       </c>
-      <c r="D322">
+      <c r="D322" s="2">
         <v>2027</v>
       </c>
       <c r="E322" t="s">
@@ -12430,9 +12433,9 @@
         <v>848</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B323" t="s">
         <v>849</v>
@@ -12440,7 +12443,7 @@
       <c r="C323" t="s">
         <v>717</v>
       </c>
-      <c r="D323">
+      <c r="D323" s="2">
         <v>2027</v>
       </c>
       <c r="E323" t="s">
@@ -12459,9 +12462,9 @@
         <v>851</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B324" t="s">
         <v>852</v>
@@ -12469,7 +12472,7 @@
       <c r="C324" t="s">
         <v>717</v>
       </c>
-      <c r="D324">
+      <c r="D324" s="2">
         <v>2027</v>
       </c>
       <c r="E324" t="s">
@@ -12488,9 +12491,9 @@
         <v>854</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B325" t="s">
         <v>855</v>
@@ -12498,7 +12501,7 @@
       <c r="C325" t="s">
         <v>717</v>
       </c>
-      <c r="D325">
+      <c r="D325" s="2">
         <v>2027</v>
       </c>
       <c r="E325" t="s">
@@ -12517,9 +12520,9 @@
         <v>857</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B326" t="s">
         <v>858</v>
@@ -12527,7 +12530,7 @@
       <c r="C326" t="s">
         <v>717</v>
       </c>
-      <c r="D326">
+      <c r="D326" s="2">
         <v>2027</v>
       </c>
       <c r="E326" t="s">
@@ -12546,9 +12549,9 @@
         <v>860</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B327" t="s">
         <v>861</v>
@@ -12556,7 +12559,7 @@
       <c r="C327" t="s">
         <v>717</v>
       </c>
-      <c r="D327">
+      <c r="D327" s="2">
         <v>2027</v>
       </c>
       <c r="E327" t="s">
@@ -12575,9 +12578,9 @@
         <v>862</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="B328" t="s">
         <v>863</v>
@@ -12585,7 +12588,7 @@
       <c r="C328" t="s">
         <v>717</v>
       </c>
-      <c r="D328">
+      <c r="D328" s="2">
         <v>2027</v>
       </c>
       <c r="E328" t="s">
@@ -12604,7 +12607,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>9</v>
       </c>
@@ -12633,7 +12636,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>9</v>
       </c>
@@ -12662,7 +12665,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>9</v>
       </c>
@@ -12691,9 +12694,9 @@
         <v>872</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B332" t="s">
         <v>873</v>
@@ -12720,9 +12723,9 @@
         <v>874</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B333" t="s">
         <v>875</v>
@@ -12749,9 +12752,9 @@
         <v>876</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B334" t="s">
         <v>877</v>
@@ -12778,9 +12781,9 @@
         <v>878</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B335" t="s">
         <v>879</v>
@@ -12807,7 +12810,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>9</v>
       </c>
@@ -12836,7 +12839,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>9</v>
       </c>
@@ -12869,10 +12872,7 @@
   <autoFilter ref="A1:I337" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="ID"/>
-        <filter val="NV"/>
         <filter val="TX"/>
-        <filter val="WA"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -12886,12 +12886,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>885</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>888</v>
       </c>

--- a/data/marketplace/MarketplacePlansData.xlsx
+++ b/data/marketplace/MarketplacePlansData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/seeram_tarunvardhan_molinahealthcare_com/Documents/Desktop/Automationss/IMP/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_95EE763EA5C74F31F8D301139C6A6534037FAE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1AF6170-09A8-4D04-BA17-59C4384E566F}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_95EE763EA5C74F31F8D301139C6A6534037FAE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E36A405D-472B-4A97-9FA0-35329F344875}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="890">
   <si>
     <t>Run</t>
   </si>
@@ -1092,9 +1092,6 @@
   </si>
   <si>
     <t>Schedule of Benefits – Silver 94 HMO - Marketplace 2027</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>TC327 Platinum 90 HMO CA-2027</t>
@@ -2763,6 +2760,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3087,7 +3088,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I337"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3124,7 +3124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -6981,12 +6981,12 @@
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C135" t="s">
         <v>329</v>
@@ -6995,27 +6995,27 @@
         <v>2027</v>
       </c>
       <c r="E135" t="s">
+        <v>357</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
         <v>358</v>
       </c>
-      <c r="F135" t="s">
-        <v>14</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>359</v>
       </c>
-      <c r="H135" t="s">
+      <c r="I135" t="s">
         <v>360</v>
       </c>
-      <c r="I135" t="s">
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>9</v>
-      </c>
-      <c r="B136" t="s">
-        <v>362</v>
       </c>
       <c r="C136" t="s">
         <v>329</v>
@@ -7024,27 +7024,27 @@
         <v>2027</v>
       </c>
       <c r="E136" t="s">
+        <v>357</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
         <v>358</v>
       </c>
-      <c r="F136" t="s">
-        <v>14</v>
-      </c>
-      <c r="G136" t="s">
-        <v>359</v>
-      </c>
       <c r="H136" t="s">
+        <v>362</v>
+      </c>
+      <c r="I136" t="s">
         <v>363</v>
       </c>
-      <c r="I136" t="s">
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>9</v>
-      </c>
-      <c r="B137" t="s">
-        <v>365</v>
       </c>
       <c r="C137" t="s">
         <v>329</v>
@@ -7053,27 +7053,27 @@
         <v>2027</v>
       </c>
       <c r="E137" t="s">
+        <v>357</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
         <v>358</v>
       </c>
-      <c r="F137" t="s">
-        <v>14</v>
-      </c>
-      <c r="G137" t="s">
-        <v>359</v>
-      </c>
       <c r="H137" t="s">
+        <v>365</v>
+      </c>
+      <c r="I137" t="s">
         <v>366</v>
       </c>
-      <c r="I137" t="s">
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
         <v>367</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>9</v>
-      </c>
-      <c r="B138" t="s">
-        <v>368</v>
       </c>
       <c r="C138" t="s">
         <v>329</v>
@@ -7082,27 +7082,27 @@
         <v>2027</v>
       </c>
       <c r="E138" t="s">
+        <v>357</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
         <v>358</v>
       </c>
-      <c r="F138" t="s">
-        <v>14</v>
-      </c>
-      <c r="G138" t="s">
-        <v>359</v>
-      </c>
       <c r="H138" t="s">
+        <v>368</v>
+      </c>
+      <c r="I138" t="s">
         <v>369</v>
       </c>
-      <c r="I138" t="s">
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>9</v>
-      </c>
-      <c r="B139" t="s">
-        <v>371</v>
       </c>
       <c r="C139" t="s">
         <v>329</v>
@@ -7111,27 +7111,27 @@
         <v>2027</v>
       </c>
       <c r="E139" t="s">
+        <v>357</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
         <v>358</v>
       </c>
-      <c r="F139" t="s">
-        <v>14</v>
-      </c>
-      <c r="G139" t="s">
-        <v>359</v>
-      </c>
       <c r="H139" t="s">
+        <v>371</v>
+      </c>
+      <c r="I139" t="s">
         <v>372</v>
       </c>
-      <c r="I139" t="s">
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="B140" t="s">
-        <v>374</v>
       </c>
       <c r="C140" t="s">
         <v>329</v>
@@ -7140,27 +7140,27 @@
         <v>2027</v>
       </c>
       <c r="E140" t="s">
+        <v>357</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
         <v>358</v>
       </c>
-      <c r="F140" t="s">
-        <v>14</v>
-      </c>
-      <c r="G140" t="s">
-        <v>359</v>
-      </c>
       <c r="H140" t="s">
+        <v>374</v>
+      </c>
+      <c r="I140" t="s">
         <v>375</v>
       </c>
-      <c r="I140" t="s">
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" t="s">
         <v>376</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="B141" t="s">
-        <v>377</v>
       </c>
       <c r="C141" t="s">
         <v>329</v>
@@ -7169,27 +7169,27 @@
         <v>2027</v>
       </c>
       <c r="E141" t="s">
+        <v>357</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
         <v>358</v>
       </c>
-      <c r="F141" t="s">
-        <v>14</v>
-      </c>
-      <c r="G141" t="s">
-        <v>359</v>
-      </c>
       <c r="H141" t="s">
+        <v>377</v>
+      </c>
+      <c r="I141" t="s">
         <v>378</v>
       </c>
-      <c r="I141" t="s">
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="B142" t="s">
-        <v>380</v>
       </c>
       <c r="C142" t="s">
         <v>329</v>
@@ -7198,27 +7198,27 @@
         <v>2027</v>
       </c>
       <c r="E142" t="s">
+        <v>357</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
         <v>358</v>
       </c>
-      <c r="F142" t="s">
-        <v>14</v>
-      </c>
-      <c r="G142" t="s">
-        <v>359</v>
-      </c>
       <c r="H142" t="s">
+        <v>380</v>
+      </c>
+      <c r="I142" t="s">
         <v>381</v>
       </c>
-      <c r="I142" t="s">
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" t="s">
         <v>382</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143" t="s">
-        <v>383</v>
       </c>
       <c r="C143" t="s">
         <v>329</v>
@@ -7227,27 +7227,27 @@
         <v>2027</v>
       </c>
       <c r="E143" t="s">
+        <v>357</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
         <v>358</v>
       </c>
-      <c r="F143" t="s">
-        <v>14</v>
-      </c>
-      <c r="G143" t="s">
-        <v>359</v>
-      </c>
       <c r="H143" t="s">
+        <v>383</v>
+      </c>
+      <c r="I143" t="s">
         <v>384</v>
       </c>
-      <c r="I143" t="s">
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="B144" t="s">
-        <v>386</v>
       </c>
       <c r="C144" t="s">
         <v>329</v>
@@ -7256,27 +7256,27 @@
         <v>2027</v>
       </c>
       <c r="E144" t="s">
+        <v>357</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
         <v>358</v>
       </c>
-      <c r="F144" t="s">
-        <v>14</v>
-      </c>
-      <c r="G144" t="s">
-        <v>359</v>
-      </c>
       <c r="H144" t="s">
+        <v>386</v>
+      </c>
+      <c r="I144" t="s">
         <v>387</v>
       </c>
-      <c r="I144" t="s">
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" t="s">
         <v>388</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>9</v>
-      </c>
-      <c r="B145" t="s">
-        <v>389</v>
       </c>
       <c r="C145" t="s">
         <v>329</v>
@@ -7285,27 +7285,27 @@
         <v>2027</v>
       </c>
       <c r="E145" t="s">
+        <v>357</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
         <v>358</v>
       </c>
-      <c r="F145" t="s">
-        <v>14</v>
-      </c>
-      <c r="G145" t="s">
-        <v>359</v>
-      </c>
       <c r="H145" t="s">
+        <v>389</v>
+      </c>
+      <c r="I145" t="s">
         <v>390</v>
       </c>
-      <c r="I145" t="s">
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" t="s">
         <v>391</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="B146" t="s">
-        <v>392</v>
       </c>
       <c r="C146" t="s">
         <v>329</v>
@@ -7314,27 +7314,27 @@
         <v>2027</v>
       </c>
       <c r="E146" t="s">
+        <v>357</v>
+      </c>
+      <c r="F146" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s">
         <v>358</v>
       </c>
-      <c r="F146" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" t="s">
-        <v>359</v>
-      </c>
       <c r="H146" t="s">
+        <v>392</v>
+      </c>
+      <c r="I146" t="s">
         <v>393</v>
       </c>
-      <c r="I146" t="s">
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" t="s">
         <v>394</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="B147" t="s">
-        <v>395</v>
       </c>
       <c r="C147" t="s">
         <v>329</v>
@@ -7343,1248 +7343,1248 @@
         <v>2027</v>
       </c>
       <c r="E147" t="s">
+        <v>357</v>
+      </c>
+      <c r="F147" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" t="s">
         <v>358</v>
       </c>
-      <c r="F147" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" t="s">
-        <v>359</v>
-      </c>
       <c r="H147" t="s">
+        <v>395</v>
+      </c>
+      <c r="I147" t="s">
         <v>396</v>
       </c>
-      <c r="I147" t="s">
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>398</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
         <v>399</v>
       </c>
-      <c r="D148" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" t="s">
-        <v>13</v>
-      </c>
-      <c r="F148" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" t="s">
+      <c r="I148" t="s">
         <v>400</v>
       </c>
-      <c r="I148" t="s">
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>9</v>
-      </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
+        <v>398</v>
+      </c>
+      <c r="D149" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" t="s">
         <v>402</v>
       </c>
-      <c r="C149" t="s">
-        <v>399</v>
-      </c>
-      <c r="D149" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" t="s">
-        <v>13</v>
-      </c>
-      <c r="F149" t="s">
-        <v>14</v>
-      </c>
-      <c r="G149" t="s">
-        <v>15</v>
-      </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>403</v>
       </c>
-      <c r="I149" t="s">
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>9</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
+        <v>398</v>
+      </c>
+      <c r="D150" t="s">
+        <v>12</v>
+      </c>
+      <c r="E150" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
         <v>405</v>
       </c>
-      <c r="C150" t="s">
-        <v>399</v>
-      </c>
-      <c r="D150" t="s">
-        <v>12</v>
-      </c>
-      <c r="E150" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>406</v>
       </c>
-      <c r="I150" t="s">
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>9</v>
-      </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
+        <v>398</v>
+      </c>
+      <c r="D151" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
         <v>408</v>
       </c>
-      <c r="C151" t="s">
-        <v>399</v>
-      </c>
-      <c r="D151" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" t="s">
-        <v>14</v>
-      </c>
-      <c r="G151" t="s">
-        <v>15</v>
-      </c>
-      <c r="H151" t="s">
+      <c r="I151" t="s">
         <v>409</v>
       </c>
-      <c r="I151" t="s">
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>9</v>
-      </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
+        <v>398</v>
+      </c>
+      <c r="D152" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" t="s">
         <v>411</v>
       </c>
-      <c r="C152" t="s">
-        <v>399</v>
-      </c>
-      <c r="D152" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" t="s">
-        <v>13</v>
-      </c>
-      <c r="F152" t="s">
-        <v>14</v>
-      </c>
-      <c r="G152" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
         <v>412</v>
       </c>
-      <c r="I152" t="s">
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>9</v>
-      </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
+        <v>398</v>
+      </c>
+      <c r="D153" t="s">
+        <v>12</v>
+      </c>
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" t="s">
         <v>414</v>
       </c>
-      <c r="C153" t="s">
-        <v>399</v>
-      </c>
-      <c r="D153" t="s">
-        <v>12</v>
-      </c>
-      <c r="E153" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" t="s">
-        <v>14</v>
-      </c>
-      <c r="G153" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" t="s">
+      <c r="I153" t="s">
         <v>415</v>
       </c>
-      <c r="I153" t="s">
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>9</v>
-      </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
+        <v>398</v>
+      </c>
+      <c r="D154" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" t="s">
         <v>417</v>
       </c>
-      <c r="C154" t="s">
-        <v>399</v>
-      </c>
-      <c r="D154" t="s">
-        <v>12</v>
-      </c>
-      <c r="E154" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>418</v>
       </c>
-      <c r="I154" t="s">
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>9</v>
-      </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
+        <v>398</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="s">
         <v>420</v>
       </c>
-      <c r="C155" t="s">
-        <v>399</v>
-      </c>
-      <c r="D155" t="s">
-        <v>12</v>
-      </c>
-      <c r="E155" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" t="s">
-        <v>14</v>
-      </c>
-      <c r="G155" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
         <v>421</v>
       </c>
-      <c r="I155" t="s">
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>9</v>
-      </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
+        <v>398</v>
+      </c>
+      <c r="D156" t="s">
+        <v>12</v>
+      </c>
+      <c r="E156" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" t="s">
         <v>423</v>
       </c>
-      <c r="C156" t="s">
-        <v>399</v>
-      </c>
-      <c r="D156" t="s">
-        <v>12</v>
-      </c>
-      <c r="E156" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" t="s">
-        <v>14</v>
-      </c>
-      <c r="G156" t="s">
-        <v>15</v>
-      </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>424</v>
       </c>
-      <c r="I156" t="s">
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>9</v>
-      </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
+        <v>398</v>
+      </c>
+      <c r="D157" t="s">
+        <v>12</v>
+      </c>
+      <c r="E157" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" t="s">
         <v>426</v>
       </c>
-      <c r="C157" t="s">
-        <v>399</v>
-      </c>
-      <c r="D157" t="s">
-        <v>12</v>
-      </c>
-      <c r="E157" t="s">
-        <v>13</v>
-      </c>
-      <c r="F157" t="s">
-        <v>14</v>
-      </c>
-      <c r="G157" t="s">
-        <v>15</v>
-      </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
         <v>427</v>
       </c>
-      <c r="I157" t="s">
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>9</v>
-      </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
+        <v>398</v>
+      </c>
+      <c r="D158" t="s">
+        <v>12</v>
+      </c>
+      <c r="E158" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
         <v>429</v>
       </c>
-      <c r="C158" t="s">
-        <v>399</v>
-      </c>
-      <c r="D158" t="s">
-        <v>12</v>
-      </c>
-      <c r="E158" t="s">
-        <v>13</v>
-      </c>
-      <c r="F158" t="s">
-        <v>14</v>
-      </c>
-      <c r="G158" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
         <v>430</v>
       </c>
-      <c r="I158" t="s">
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>9</v>
-      </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
+        <v>398</v>
+      </c>
+      <c r="D159" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="s">
         <v>432</v>
       </c>
-      <c r="C159" t="s">
-        <v>399</v>
-      </c>
-      <c r="D159" t="s">
-        <v>12</v>
-      </c>
-      <c r="E159" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" t="s">
-        <v>14</v>
-      </c>
-      <c r="G159" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" t="s">
+      <c r="I159" t="s">
         <v>433</v>
       </c>
-      <c r="I159" t="s">
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>9</v>
-      </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
+        <v>398</v>
+      </c>
+      <c r="D160" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" t="s">
         <v>435</v>
       </c>
-      <c r="C160" t="s">
-        <v>399</v>
-      </c>
-      <c r="D160" t="s">
-        <v>12</v>
-      </c>
-      <c r="E160" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" t="s">
-        <v>14</v>
-      </c>
-      <c r="G160" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
         <v>436</v>
       </c>
-      <c r="I160" t="s">
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>9</v>
-      </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
+        <v>398</v>
+      </c>
+      <c r="D161" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" t="s">
+        <v>14</v>
+      </c>
+      <c r="G161" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" t="s">
         <v>438</v>
       </c>
-      <c r="C161" t="s">
-        <v>399</v>
-      </c>
-      <c r="D161" t="s">
-        <v>12</v>
-      </c>
-      <c r="E161" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" t="s">
-        <v>14</v>
-      </c>
-      <c r="G161" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" t="s">
+      <c r="I161" t="s">
         <v>439</v>
       </c>
-      <c r="I161" t="s">
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>9</v>
-      </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
+        <v>398</v>
+      </c>
+      <c r="D162" t="s">
+        <v>12</v>
+      </c>
+      <c r="E162" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="s">
         <v>441</v>
       </c>
-      <c r="C162" t="s">
-        <v>399</v>
-      </c>
-      <c r="D162" t="s">
-        <v>12</v>
-      </c>
-      <c r="E162" t="s">
-        <v>13</v>
-      </c>
-      <c r="F162" t="s">
-        <v>14</v>
-      </c>
-      <c r="G162" t="s">
-        <v>15</v>
-      </c>
-      <c r="H162" t="s">
+      <c r="I162" t="s">
         <v>442</v>
       </c>
-      <c r="I162" t="s">
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>9</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>444</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" t="s">
+        <v>14</v>
+      </c>
+      <c r="G163" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" t="s">
         <v>445</v>
       </c>
-      <c r="D163" t="s">
-        <v>12</v>
-      </c>
-      <c r="E163" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" t="s">
-        <v>14</v>
-      </c>
-      <c r="G163" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>446</v>
       </c>
-      <c r="I163" t="s">
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>9</v>
-      </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
+        <v>444</v>
+      </c>
+      <c r="D164" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" t="s">
         <v>448</v>
       </c>
-      <c r="C164" t="s">
-        <v>445</v>
-      </c>
-      <c r="D164" t="s">
-        <v>12</v>
-      </c>
-      <c r="E164" t="s">
-        <v>13</v>
-      </c>
-      <c r="F164" t="s">
-        <v>14</v>
-      </c>
-      <c r="G164" t="s">
-        <v>15</v>
-      </c>
-      <c r="H164" t="s">
+      <c r="I164" t="s">
         <v>449</v>
       </c>
-      <c r="I164" t="s">
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>9</v>
-      </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
+        <v>444</v>
+      </c>
+      <c r="D165" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" t="s">
+        <v>14</v>
+      </c>
+      <c r="G165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
         <v>451</v>
       </c>
-      <c r="C165" t="s">
-        <v>445</v>
-      </c>
-      <c r="D165" t="s">
-        <v>12</v>
-      </c>
-      <c r="E165" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" t="s">
-        <v>14</v>
-      </c>
-      <c r="G165" t="s">
-        <v>15</v>
-      </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
         <v>452</v>
       </c>
-      <c r="I165" t="s">
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>9</v>
-      </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
+        <v>444</v>
+      </c>
+      <c r="D166" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" t="s">
+        <v>14</v>
+      </c>
+      <c r="G166" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" t="s">
         <v>454</v>
       </c>
-      <c r="C166" t="s">
-        <v>445</v>
-      </c>
-      <c r="D166" t="s">
-        <v>12</v>
-      </c>
-      <c r="E166" t="s">
-        <v>13</v>
-      </c>
-      <c r="F166" t="s">
-        <v>14</v>
-      </c>
-      <c r="G166" t="s">
-        <v>15</v>
-      </c>
-      <c r="H166" t="s">
+      <c r="I166" t="s">
         <v>455</v>
       </c>
-      <c r="I166" t="s">
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>9</v>
-      </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
+        <v>444</v>
+      </c>
+      <c r="D167" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" t="s">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" t="s">
         <v>457</v>
       </c>
-      <c r="C167" t="s">
-        <v>445</v>
-      </c>
-      <c r="D167" t="s">
-        <v>12</v>
-      </c>
-      <c r="E167" t="s">
-        <v>13</v>
-      </c>
-      <c r="F167" t="s">
-        <v>14</v>
-      </c>
-      <c r="G167" t="s">
-        <v>15</v>
-      </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
         <v>458</v>
       </c>
-      <c r="I167" t="s">
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>9</v>
-      </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
+        <v>444</v>
+      </c>
+      <c r="D168" t="s">
+        <v>12</v>
+      </c>
+      <c r="E168" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" t="s">
+        <v>14</v>
+      </c>
+      <c r="G168" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" t="s">
         <v>460</v>
       </c>
-      <c r="C168" t="s">
-        <v>445</v>
-      </c>
-      <c r="D168" t="s">
-        <v>12</v>
-      </c>
-      <c r="E168" t="s">
-        <v>13</v>
-      </c>
-      <c r="F168" t="s">
-        <v>14</v>
-      </c>
-      <c r="G168" t="s">
-        <v>15</v>
-      </c>
-      <c r="H168" t="s">
+      <c r="I168" t="s">
         <v>461</v>
       </c>
-      <c r="I168" t="s">
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>9</v>
-      </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
+        <v>444</v>
+      </c>
+      <c r="D169" t="s">
+        <v>12</v>
+      </c>
+      <c r="E169" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" t="s">
         <v>463</v>
       </c>
-      <c r="C169" t="s">
-        <v>445</v>
-      </c>
-      <c r="D169" t="s">
-        <v>12</v>
-      </c>
-      <c r="E169" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" t="s">
-        <v>14</v>
-      </c>
-      <c r="G169" t="s">
-        <v>15</v>
-      </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
         <v>464</v>
       </c>
-      <c r="I169" t="s">
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>9</v>
-      </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
+        <v>444</v>
+      </c>
+      <c r="D170" t="s">
+        <v>12</v>
+      </c>
+      <c r="E170" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" t="s">
         <v>466</v>
       </c>
-      <c r="C170" t="s">
-        <v>445</v>
-      </c>
-      <c r="D170" t="s">
-        <v>12</v>
-      </c>
-      <c r="E170" t="s">
-        <v>13</v>
-      </c>
-      <c r="F170" t="s">
-        <v>14</v>
-      </c>
-      <c r="G170" t="s">
-        <v>15</v>
-      </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>467</v>
       </c>
-      <c r="I170" t="s">
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>9</v>
-      </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
+        <v>444</v>
+      </c>
+      <c r="D171" t="s">
+        <v>12</v>
+      </c>
+      <c r="E171" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" t="s">
         <v>469</v>
       </c>
-      <c r="C171" t="s">
-        <v>445</v>
-      </c>
-      <c r="D171" t="s">
-        <v>12</v>
-      </c>
-      <c r="E171" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" t="s">
-        <v>14</v>
-      </c>
-      <c r="G171" t="s">
-        <v>15</v>
-      </c>
-      <c r="H171" t="s">
+      <c r="I171" t="s">
         <v>470</v>
       </c>
-      <c r="I171" t="s">
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>9</v>
-      </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
+        <v>444</v>
+      </c>
+      <c r="D172" t="s">
+        <v>12</v>
+      </c>
+      <c r="E172" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" t="s">
         <v>472</v>
       </c>
-      <c r="C172" t="s">
-        <v>445</v>
-      </c>
-      <c r="D172" t="s">
-        <v>12</v>
-      </c>
-      <c r="E172" t="s">
-        <v>13</v>
-      </c>
-      <c r="F172" t="s">
-        <v>14</v>
-      </c>
-      <c r="G172" t="s">
-        <v>15</v>
-      </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>473</v>
       </c>
-      <c r="I172" t="s">
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>9</v>
-      </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
+        <v>444</v>
+      </c>
+      <c r="D173" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" t="s">
+        <v>14</v>
+      </c>
+      <c r="G173" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" t="s">
         <v>475</v>
       </c>
-      <c r="C173" t="s">
-        <v>445</v>
-      </c>
-      <c r="D173" t="s">
-        <v>12</v>
-      </c>
-      <c r="E173" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" t="s">
-        <v>14</v>
-      </c>
-      <c r="G173" t="s">
-        <v>15</v>
-      </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>476</v>
       </c>
-      <c r="I173" t="s">
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>9</v>
-      </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
+        <v>444</v>
+      </c>
+      <c r="D174" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" t="s">
+        <v>14</v>
+      </c>
+      <c r="G174" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" t="s">
         <v>478</v>
       </c>
-      <c r="C174" t="s">
-        <v>445</v>
-      </c>
-      <c r="D174" t="s">
-        <v>12</v>
-      </c>
-      <c r="E174" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" t="s">
-        <v>14</v>
-      </c>
-      <c r="G174" t="s">
-        <v>15</v>
-      </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>479</v>
       </c>
-      <c r="I174" t="s">
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>9</v>
-      </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
+        <v>444</v>
+      </c>
+      <c r="D175" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+      <c r="G175" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" t="s">
         <v>481</v>
       </c>
-      <c r="C175" t="s">
-        <v>445</v>
-      </c>
-      <c r="D175" t="s">
-        <v>12</v>
-      </c>
-      <c r="E175" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" t="s">
-        <v>14</v>
-      </c>
-      <c r="G175" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" t="s">
+      <c r="I175" t="s">
         <v>482</v>
       </c>
-      <c r="I175" t="s">
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>9</v>
-      </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
+        <v>444</v>
+      </c>
+      <c r="D176" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" t="s">
+        <v>14</v>
+      </c>
+      <c r="G176" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" t="s">
         <v>484</v>
       </c>
-      <c r="C176" t="s">
-        <v>445</v>
-      </c>
-      <c r="D176" t="s">
-        <v>12</v>
-      </c>
-      <c r="E176" t="s">
-        <v>13</v>
-      </c>
-      <c r="F176" t="s">
-        <v>14</v>
-      </c>
-      <c r="G176" t="s">
-        <v>15</v>
-      </c>
-      <c r="H176" t="s">
+      <c r="I176" t="s">
         <v>485</v>
       </c>
-      <c r="I176" t="s">
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>9</v>
-      </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
+        <v>444</v>
+      </c>
+      <c r="D177" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" t="s">
+        <v>14</v>
+      </c>
+      <c r="G177" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" t="s">
         <v>487</v>
       </c>
-      <c r="C177" t="s">
-        <v>445</v>
-      </c>
-      <c r="D177" t="s">
-        <v>12</v>
-      </c>
-      <c r="E177" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" t="s">
-        <v>14</v>
-      </c>
-      <c r="G177" t="s">
-        <v>15</v>
-      </c>
-      <c r="H177" t="s">
+      <c r="I177" t="s">
         <v>488</v>
       </c>
-      <c r="I177" t="s">
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>9</v>
-      </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
+        <v>444</v>
+      </c>
+      <c r="D178" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178" t="s">
+        <v>15</v>
+      </c>
+      <c r="H178" t="s">
         <v>490</v>
       </c>
-      <c r="C178" t="s">
-        <v>445</v>
-      </c>
-      <c r="D178" t="s">
-        <v>12</v>
-      </c>
-      <c r="E178" t="s">
-        <v>13</v>
-      </c>
-      <c r="F178" t="s">
-        <v>14</v>
-      </c>
-      <c r="G178" t="s">
-        <v>15</v>
-      </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>491</v>
       </c>
-      <c r="I178" t="s">
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>9</v>
-      </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
+        <v>444</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
+      </c>
+      <c r="E179" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" t="s">
+        <v>14</v>
+      </c>
+      <c r="G179" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" t="s">
         <v>493</v>
       </c>
-      <c r="C179" t="s">
-        <v>445</v>
-      </c>
-      <c r="D179" t="s">
-        <v>12</v>
-      </c>
-      <c r="E179" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" t="s">
-        <v>14</v>
-      </c>
-      <c r="G179" t="s">
-        <v>15</v>
-      </c>
-      <c r="H179" t="s">
+      <c r="I179" t="s">
         <v>494</v>
       </c>
-      <c r="I179" t="s">
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>9</v>
-      </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
+        <v>444</v>
+      </c>
+      <c r="D180" t="s">
+        <v>12</v>
+      </c>
+      <c r="E180" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" t="s">
+        <v>14</v>
+      </c>
+      <c r="G180" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" t="s">
         <v>496</v>
       </c>
-      <c r="C180" t="s">
-        <v>445</v>
-      </c>
-      <c r="D180" t="s">
-        <v>12</v>
-      </c>
-      <c r="E180" t="s">
-        <v>13</v>
-      </c>
-      <c r="F180" t="s">
-        <v>14</v>
-      </c>
-      <c r="G180" t="s">
-        <v>15</v>
-      </c>
-      <c r="H180" t="s">
+      <c r="I180" t="s">
         <v>497</v>
       </c>
-      <c r="I180" t="s">
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>9</v>
-      </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
+        <v>444</v>
+      </c>
+      <c r="D181" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" t="s">
+        <v>14</v>
+      </c>
+      <c r="G181" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" t="s">
         <v>499</v>
       </c>
-      <c r="C181" t="s">
-        <v>445</v>
-      </c>
-      <c r="D181" t="s">
-        <v>12</v>
-      </c>
-      <c r="E181" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" t="s">
-        <v>14</v>
-      </c>
-      <c r="G181" t="s">
-        <v>15</v>
-      </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>500</v>
       </c>
-      <c r="I181" t="s">
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>9</v>
-      </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
+        <v>444</v>
+      </c>
+      <c r="D182" t="s">
+        <v>12</v>
+      </c>
+      <c r="E182" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" t="s">
+        <v>14</v>
+      </c>
+      <c r="G182" t="s">
+        <v>15</v>
+      </c>
+      <c r="H182" t="s">
         <v>502</v>
       </c>
-      <c r="C182" t="s">
-        <v>445</v>
-      </c>
-      <c r="D182" t="s">
-        <v>12</v>
-      </c>
-      <c r="E182" t="s">
-        <v>13</v>
-      </c>
-      <c r="F182" t="s">
-        <v>14</v>
-      </c>
-      <c r="G182" t="s">
-        <v>15</v>
-      </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>503</v>
       </c>
-      <c r="I182" t="s">
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>9</v>
-      </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
+        <v>444</v>
+      </c>
+      <c r="D183" t="s">
+        <v>12</v>
+      </c>
+      <c r="E183" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" t="s">
+        <v>14</v>
+      </c>
+      <c r="G183" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" t="s">
         <v>505</v>
       </c>
-      <c r="C183" t="s">
-        <v>445</v>
-      </c>
-      <c r="D183" t="s">
-        <v>12</v>
-      </c>
-      <c r="E183" t="s">
-        <v>13</v>
-      </c>
-      <c r="F183" t="s">
-        <v>14</v>
-      </c>
-      <c r="G183" t="s">
-        <v>15</v>
-      </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>506</v>
       </c>
-      <c r="I183" t="s">
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>9</v>
-      </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
+        <v>444</v>
+      </c>
+      <c r="D184" t="s">
+        <v>12</v>
+      </c>
+      <c r="E184" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" t="s">
+        <v>14</v>
+      </c>
+      <c r="G184" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" t="s">
         <v>508</v>
       </c>
-      <c r="C184" t="s">
-        <v>445</v>
-      </c>
-      <c r="D184" t="s">
-        <v>12</v>
-      </c>
-      <c r="E184" t="s">
-        <v>13</v>
-      </c>
-      <c r="F184" t="s">
-        <v>14</v>
-      </c>
-      <c r="G184" t="s">
-        <v>15</v>
-      </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>509</v>
       </c>
-      <c r="I184" t="s">
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>9</v>
-      </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
+        <v>444</v>
+      </c>
+      <c r="D185" t="s">
+        <v>12</v>
+      </c>
+      <c r="E185" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+      <c r="G185" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" t="s">
         <v>511</v>
       </c>
-      <c r="C185" t="s">
-        <v>445</v>
-      </c>
-      <c r="D185" t="s">
-        <v>12</v>
-      </c>
-      <c r="E185" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" t="s">
-        <v>14</v>
-      </c>
-      <c r="G185" t="s">
-        <v>15</v>
-      </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>512</v>
       </c>
-      <c r="I185" t="s">
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>9</v>
-      </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
+        <v>444</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+      <c r="G186" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" t="s">
         <v>514</v>
       </c>
-      <c r="C186" t="s">
-        <v>445</v>
-      </c>
-      <c r="D186" t="s">
-        <v>12</v>
-      </c>
-      <c r="E186" t="s">
-        <v>13</v>
-      </c>
-      <c r="F186" t="s">
-        <v>14</v>
-      </c>
-      <c r="G186" t="s">
-        <v>15</v>
-      </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>515</v>
       </c>
-      <c r="I186" t="s">
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>9</v>
-      </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
+        <v>444</v>
+      </c>
+      <c r="D187" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+      <c r="G187" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" t="s">
         <v>517</v>
       </c>
-      <c r="C187" t="s">
-        <v>445</v>
-      </c>
-      <c r="D187" t="s">
-        <v>12</v>
-      </c>
-      <c r="E187" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" t="s">
-        <v>14</v>
-      </c>
-      <c r="G187" t="s">
-        <v>15</v>
-      </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>518</v>
       </c>
-      <c r="I187" t="s">
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>9</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
+        <v>444</v>
+      </c>
+      <c r="D188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E188" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+      <c r="G188" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" t="s">
         <v>520</v>
       </c>
-      <c r="C188" t="s">
-        <v>445</v>
-      </c>
-      <c r="D188" t="s">
-        <v>12</v>
-      </c>
-      <c r="E188" t="s">
-        <v>13</v>
-      </c>
-      <c r="F188" t="s">
-        <v>14</v>
-      </c>
-      <c r="G188" t="s">
-        <v>15</v>
-      </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>521</v>
       </c>
-      <c r="I188" t="s">
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B189" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>9</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
+        <v>444</v>
+      </c>
+      <c r="D189" t="s">
+        <v>12</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+      <c r="G189" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" t="s">
         <v>523</v>
       </c>
-      <c r="C189" t="s">
-        <v>445</v>
-      </c>
-      <c r="D189" t="s">
-        <v>12</v>
-      </c>
-      <c r="E189" t="s">
-        <v>13</v>
-      </c>
-      <c r="F189" t="s">
-        <v>14</v>
-      </c>
-      <c r="G189" t="s">
-        <v>15</v>
-      </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>524</v>
       </c>
-      <c r="I189" t="s">
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>9</v>
+      </c>
+      <c r="B190" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>9</v>
-      </c>
-      <c r="B190" t="s">
-        <v>526</v>
-      </c>
       <c r="C190" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D190" t="s">
         <v>12</v>
@@ -8602,18 +8602,18 @@
         <v>64</v>
       </c>
       <c r="I190" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>9</v>
+      </c>
+      <c r="B191" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>9</v>
-      </c>
-      <c r="B191" t="s">
-        <v>528</v>
-      </c>
       <c r="C191" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D191" t="s">
         <v>12</v>
@@ -8631,1265 +8631,1265 @@
         <v>67</v>
       </c>
       <c r="I191" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>9</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>530</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" t="s">
+        <v>14</v>
+      </c>
+      <c r="G192" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" t="s">
         <v>531</v>
       </c>
-      <c r="D192" t="s">
-        <v>12</v>
-      </c>
-      <c r="E192" t="s">
-        <v>13</v>
-      </c>
-      <c r="F192" t="s">
-        <v>14</v>
-      </c>
-      <c r="G192" t="s">
-        <v>15</v>
-      </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>532</v>
       </c>
-      <c r="I192" t="s">
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>9</v>
-      </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
+        <v>530</v>
+      </c>
+      <c r="D193" t="s">
+        <v>12</v>
+      </c>
+      <c r="E193" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193" t="s">
+        <v>14</v>
+      </c>
+      <c r="G193" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" t="s">
         <v>534</v>
       </c>
-      <c r="C193" t="s">
-        <v>531</v>
-      </c>
-      <c r="D193" t="s">
-        <v>12</v>
-      </c>
-      <c r="E193" t="s">
-        <v>13</v>
-      </c>
-      <c r="F193" t="s">
-        <v>14</v>
-      </c>
-      <c r="G193" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>535</v>
       </c>
-      <c r="I193" t="s">
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>9</v>
-      </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
+        <v>530</v>
+      </c>
+      <c r="D194" t="s">
+        <v>12</v>
+      </c>
+      <c r="E194" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" t="s">
+        <v>14</v>
+      </c>
+      <c r="G194" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" t="s">
         <v>537</v>
       </c>
-      <c r="C194" t="s">
-        <v>531</v>
-      </c>
-      <c r="D194" t="s">
-        <v>12</v>
-      </c>
-      <c r="E194" t="s">
-        <v>13</v>
-      </c>
-      <c r="F194" t="s">
-        <v>14</v>
-      </c>
-      <c r="G194" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>538</v>
       </c>
-      <c r="I194" t="s">
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>9</v>
+      </c>
+      <c r="B195" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>9</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
+        <v>530</v>
+      </c>
+      <c r="D195" t="s">
+        <v>12</v>
+      </c>
+      <c r="E195" t="s">
+        <v>13</v>
+      </c>
+      <c r="F195" t="s">
+        <v>14</v>
+      </c>
+      <c r="G195" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" t="s">
         <v>540</v>
       </c>
-      <c r="C195" t="s">
-        <v>531</v>
-      </c>
-      <c r="D195" t="s">
-        <v>12</v>
-      </c>
-      <c r="E195" t="s">
-        <v>13</v>
-      </c>
-      <c r="F195" t="s">
-        <v>14</v>
-      </c>
-      <c r="G195" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>541</v>
       </c>
-      <c r="I195" t="s">
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>9</v>
+      </c>
+      <c r="B196" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>9</v>
-      </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
+        <v>530</v>
+      </c>
+      <c r="D196" t="s">
+        <v>12</v>
+      </c>
+      <c r="E196" t="s">
+        <v>13</v>
+      </c>
+      <c r="F196" t="s">
+        <v>14</v>
+      </c>
+      <c r="G196" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" t="s">
         <v>543</v>
       </c>
-      <c r="C196" t="s">
-        <v>531</v>
-      </c>
-      <c r="D196" t="s">
-        <v>12</v>
-      </c>
-      <c r="E196" t="s">
-        <v>13</v>
-      </c>
-      <c r="F196" t="s">
-        <v>14</v>
-      </c>
-      <c r="G196" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>544</v>
       </c>
-      <c r="I196" t="s">
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>9</v>
+      </c>
+      <c r="B197" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>9</v>
-      </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
+        <v>530</v>
+      </c>
+      <c r="D197" t="s">
+        <v>12</v>
+      </c>
+      <c r="E197" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197" t="s">
+        <v>14</v>
+      </c>
+      <c r="G197" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" t="s">
         <v>546</v>
       </c>
-      <c r="C197" t="s">
-        <v>531</v>
-      </c>
-      <c r="D197" t="s">
-        <v>12</v>
-      </c>
-      <c r="E197" t="s">
-        <v>13</v>
-      </c>
-      <c r="F197" t="s">
-        <v>14</v>
-      </c>
-      <c r="G197" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>547</v>
       </c>
-      <c r="I197" t="s">
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
-        <v>9</v>
-      </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
+        <v>530</v>
+      </c>
+      <c r="D198" t="s">
+        <v>12</v>
+      </c>
+      <c r="E198" t="s">
+        <v>13</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+      <c r="G198" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" t="s">
         <v>549</v>
       </c>
-      <c r="C198" t="s">
-        <v>531</v>
-      </c>
-      <c r="D198" t="s">
-        <v>12</v>
-      </c>
-      <c r="E198" t="s">
-        <v>13</v>
-      </c>
-      <c r="F198" t="s">
-        <v>14</v>
-      </c>
-      <c r="G198" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>550</v>
       </c>
-      <c r="I198" t="s">
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
-        <v>9</v>
-      </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
+        <v>530</v>
+      </c>
+      <c r="D199" t="s">
+        <v>12</v>
+      </c>
+      <c r="E199" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+      <c r="G199" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" t="s">
         <v>552</v>
       </c>
-      <c r="C199" t="s">
-        <v>531</v>
-      </c>
-      <c r="D199" t="s">
-        <v>12</v>
-      </c>
-      <c r="E199" t="s">
-        <v>13</v>
-      </c>
-      <c r="F199" t="s">
-        <v>14</v>
-      </c>
-      <c r="G199" t="s">
-        <v>15</v>
-      </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>553</v>
       </c>
-      <c r="I199" t="s">
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
-        <v>9</v>
-      </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
+        <v>530</v>
+      </c>
+      <c r="D200" t="s">
+        <v>12</v>
+      </c>
+      <c r="E200" t="s">
+        <v>13</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+      <c r="G200" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" t="s">
         <v>555</v>
       </c>
-      <c r="C200" t="s">
-        <v>531</v>
-      </c>
-      <c r="D200" t="s">
-        <v>12</v>
-      </c>
-      <c r="E200" t="s">
-        <v>13</v>
-      </c>
-      <c r="F200" t="s">
-        <v>14</v>
-      </c>
-      <c r="G200" t="s">
-        <v>15</v>
-      </c>
-      <c r="H200" t="s">
+      <c r="I200" t="s">
         <v>556</v>
       </c>
-      <c r="I200" t="s">
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>9</v>
-      </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
+        <v>530</v>
+      </c>
+      <c r="D201" t="s">
+        <v>12</v>
+      </c>
+      <c r="E201" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201" t="s">
+        <v>14</v>
+      </c>
+      <c r="G201" t="s">
+        <v>15</v>
+      </c>
+      <c r="H201" t="s">
         <v>558</v>
       </c>
-      <c r="C201" t="s">
-        <v>531</v>
-      </c>
-      <c r="D201" t="s">
-        <v>12</v>
-      </c>
-      <c r="E201" t="s">
-        <v>13</v>
-      </c>
-      <c r="F201" t="s">
-        <v>14</v>
-      </c>
-      <c r="G201" t="s">
-        <v>15</v>
-      </c>
-      <c r="H201" t="s">
+      <c r="I201" t="s">
         <v>559</v>
       </c>
-      <c r="I201" t="s">
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>9</v>
-      </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
+        <v>530</v>
+      </c>
+      <c r="D202" t="s">
+        <v>12</v>
+      </c>
+      <c r="E202" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" t="s">
+        <v>14</v>
+      </c>
+      <c r="G202" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" t="s">
         <v>561</v>
       </c>
-      <c r="C202" t="s">
-        <v>531</v>
-      </c>
-      <c r="D202" t="s">
-        <v>12</v>
-      </c>
-      <c r="E202" t="s">
-        <v>13</v>
-      </c>
-      <c r="F202" t="s">
-        <v>14</v>
-      </c>
-      <c r="G202" t="s">
-        <v>15</v>
-      </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>562</v>
       </c>
-      <c r="I202" t="s">
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>9</v>
-      </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
+        <v>530</v>
+      </c>
+      <c r="D203" t="s">
+        <v>12</v>
+      </c>
+      <c r="E203" t="s">
+        <v>13</v>
+      </c>
+      <c r="F203" t="s">
+        <v>14</v>
+      </c>
+      <c r="G203" t="s">
+        <v>15</v>
+      </c>
+      <c r="H203" t="s">
         <v>564</v>
       </c>
-      <c r="C203" t="s">
-        <v>531</v>
-      </c>
-      <c r="D203" t="s">
-        <v>12</v>
-      </c>
-      <c r="E203" t="s">
-        <v>13</v>
-      </c>
-      <c r="F203" t="s">
-        <v>14</v>
-      </c>
-      <c r="G203" t="s">
-        <v>15</v>
-      </c>
-      <c r="H203" t="s">
+      <c r="I203" t="s">
         <v>565</v>
       </c>
-      <c r="I203" t="s">
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>9</v>
-      </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
+        <v>530</v>
+      </c>
+      <c r="D204" t="s">
+        <v>12</v>
+      </c>
+      <c r="E204" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204" t="s">
+        <v>14</v>
+      </c>
+      <c r="G204" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" t="s">
         <v>567</v>
       </c>
-      <c r="C204" t="s">
-        <v>531</v>
-      </c>
-      <c r="D204" t="s">
-        <v>12</v>
-      </c>
-      <c r="E204" t="s">
-        <v>13</v>
-      </c>
-      <c r="F204" t="s">
-        <v>14</v>
-      </c>
-      <c r="G204" t="s">
-        <v>15</v>
-      </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>568</v>
       </c>
-      <c r="I204" t="s">
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>9</v>
-      </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
+        <v>530</v>
+      </c>
+      <c r="D205" t="s">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" t="s">
+        <v>14</v>
+      </c>
+      <c r="G205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" t="s">
         <v>570</v>
       </c>
-      <c r="C205" t="s">
-        <v>531</v>
-      </c>
-      <c r="D205" t="s">
-        <v>12</v>
-      </c>
-      <c r="E205" t="s">
-        <v>13</v>
-      </c>
-      <c r="F205" t="s">
-        <v>14</v>
-      </c>
-      <c r="G205" t="s">
-        <v>15</v>
-      </c>
-      <c r="H205" t="s">
+      <c r="I205" t="s">
         <v>571</v>
       </c>
-      <c r="I205" t="s">
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>9</v>
-      </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
+        <v>530</v>
+      </c>
+      <c r="D206" t="s">
+        <v>12</v>
+      </c>
+      <c r="E206" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>14</v>
+      </c>
+      <c r="G206" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" t="s">
         <v>573</v>
       </c>
-      <c r="C206" t="s">
-        <v>531</v>
-      </c>
-      <c r="D206" t="s">
-        <v>12</v>
-      </c>
-      <c r="E206" t="s">
-        <v>13</v>
-      </c>
-      <c r="F206" t="s">
-        <v>14</v>
-      </c>
-      <c r="G206" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" t="s">
+      <c r="I206" t="s">
         <v>574</v>
       </c>
-      <c r="I206" t="s">
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>9</v>
-      </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
+        <v>530</v>
+      </c>
+      <c r="D207" t="s">
+        <v>12</v>
+      </c>
+      <c r="E207" t="s">
+        <v>13</v>
+      </c>
+      <c r="F207" t="s">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s">
+        <v>15</v>
+      </c>
+      <c r="H207" t="s">
         <v>576</v>
       </c>
-      <c r="C207" t="s">
-        <v>531</v>
-      </c>
-      <c r="D207" t="s">
-        <v>12</v>
-      </c>
-      <c r="E207" t="s">
-        <v>13</v>
-      </c>
-      <c r="F207" t="s">
-        <v>14</v>
-      </c>
-      <c r="G207" t="s">
-        <v>15</v>
-      </c>
-      <c r="H207" t="s">
+      <c r="I207" t="s">
         <v>577</v>
       </c>
-      <c r="I207" t="s">
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>9</v>
-      </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
+        <v>530</v>
+      </c>
+      <c r="D208" t="s">
+        <v>12</v>
+      </c>
+      <c r="E208" t="s">
+        <v>13</v>
+      </c>
+      <c r="F208" t="s">
+        <v>14</v>
+      </c>
+      <c r="G208" t="s">
+        <v>15</v>
+      </c>
+      <c r="H208" t="s">
         <v>579</v>
       </c>
-      <c r="C208" t="s">
-        <v>531</v>
-      </c>
-      <c r="D208" t="s">
-        <v>12</v>
-      </c>
-      <c r="E208" t="s">
-        <v>13</v>
-      </c>
-      <c r="F208" t="s">
-        <v>14</v>
-      </c>
-      <c r="G208" t="s">
-        <v>15</v>
-      </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
         <v>580</v>
       </c>
-      <c r="I208" t="s">
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>9</v>
-      </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
+        <v>530</v>
+      </c>
+      <c r="D209" t="s">
+        <v>12</v>
+      </c>
+      <c r="E209" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209" t="s">
+        <v>14</v>
+      </c>
+      <c r="G209" t="s">
+        <v>15</v>
+      </c>
+      <c r="H209" t="s">
         <v>582</v>
       </c>
-      <c r="C209" t="s">
-        <v>531</v>
-      </c>
-      <c r="D209" t="s">
-        <v>12</v>
-      </c>
-      <c r="E209" t="s">
-        <v>13</v>
-      </c>
-      <c r="F209" t="s">
-        <v>14</v>
-      </c>
-      <c r="G209" t="s">
-        <v>15</v>
-      </c>
-      <c r="H209" t="s">
+      <c r="I209" t="s">
         <v>583</v>
       </c>
-      <c r="I209" t="s">
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
-        <v>9</v>
-      </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
+        <v>530</v>
+      </c>
+      <c r="D210" t="s">
+        <v>12</v>
+      </c>
+      <c r="E210" t="s">
+        <v>13</v>
+      </c>
+      <c r="F210" t="s">
+        <v>14</v>
+      </c>
+      <c r="G210" t="s">
+        <v>15</v>
+      </c>
+      <c r="H210" t="s">
         <v>585</v>
       </c>
-      <c r="C210" t="s">
-        <v>531</v>
-      </c>
-      <c r="D210" t="s">
-        <v>12</v>
-      </c>
-      <c r="E210" t="s">
-        <v>13</v>
-      </c>
-      <c r="F210" t="s">
-        <v>14</v>
-      </c>
-      <c r="G210" t="s">
-        <v>15</v>
-      </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>586</v>
       </c>
-      <c r="I210" t="s">
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>9</v>
-      </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
+        <v>530</v>
+      </c>
+      <c r="D211" t="s">
+        <v>12</v>
+      </c>
+      <c r="E211" t="s">
+        <v>13</v>
+      </c>
+      <c r="F211" t="s">
+        <v>14</v>
+      </c>
+      <c r="G211" t="s">
+        <v>15</v>
+      </c>
+      <c r="H211" t="s">
         <v>588</v>
       </c>
-      <c r="C211" t="s">
-        <v>531</v>
-      </c>
-      <c r="D211" t="s">
-        <v>12</v>
-      </c>
-      <c r="E211" t="s">
-        <v>13</v>
-      </c>
-      <c r="F211" t="s">
-        <v>14</v>
-      </c>
-      <c r="G211" t="s">
-        <v>15</v>
-      </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>589</v>
       </c>
-      <c r="I211" t="s">
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
-        <v>9</v>
-      </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
+        <v>530</v>
+      </c>
+      <c r="D212" t="s">
+        <v>12</v>
+      </c>
+      <c r="E212" t="s">
+        <v>13</v>
+      </c>
+      <c r="F212" t="s">
+        <v>14</v>
+      </c>
+      <c r="G212" t="s">
+        <v>15</v>
+      </c>
+      <c r="H212" t="s">
         <v>591</v>
       </c>
-      <c r="C212" t="s">
-        <v>531</v>
-      </c>
-      <c r="D212" t="s">
-        <v>12</v>
-      </c>
-      <c r="E212" t="s">
-        <v>13</v>
-      </c>
-      <c r="F212" t="s">
-        <v>14</v>
-      </c>
-      <c r="G212" t="s">
-        <v>15</v>
-      </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>592</v>
       </c>
-      <c r="I212" t="s">
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
-        <v>9</v>
-      </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
+        <v>530</v>
+      </c>
+      <c r="D213" t="s">
+        <v>12</v>
+      </c>
+      <c r="E213" t="s">
+        <v>13</v>
+      </c>
+      <c r="F213" t="s">
+        <v>14</v>
+      </c>
+      <c r="G213" t="s">
+        <v>15</v>
+      </c>
+      <c r="H213" t="s">
         <v>594</v>
       </c>
-      <c r="C213" t="s">
-        <v>531</v>
-      </c>
-      <c r="D213" t="s">
-        <v>12</v>
-      </c>
-      <c r="E213" t="s">
-        <v>13</v>
-      </c>
-      <c r="F213" t="s">
-        <v>14</v>
-      </c>
-      <c r="G213" t="s">
-        <v>15</v>
-      </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>595</v>
       </c>
-      <c r="I213" t="s">
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
-        <v>9</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
+        <v>530</v>
+      </c>
+      <c r="D214" t="s">
+        <v>12</v>
+      </c>
+      <c r="E214" t="s">
+        <v>13</v>
+      </c>
+      <c r="F214" t="s">
+        <v>14</v>
+      </c>
+      <c r="G214" t="s">
+        <v>15</v>
+      </c>
+      <c r="H214" t="s">
         <v>597</v>
       </c>
-      <c r="C214" t="s">
-        <v>531</v>
-      </c>
-      <c r="D214" t="s">
-        <v>12</v>
-      </c>
-      <c r="E214" t="s">
-        <v>13</v>
-      </c>
-      <c r="F214" t="s">
-        <v>14</v>
-      </c>
-      <c r="G214" t="s">
-        <v>15</v>
-      </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>598</v>
       </c>
-      <c r="I214" t="s">
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
-        <v>9</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
+        <v>530</v>
+      </c>
+      <c r="D215" t="s">
+        <v>12</v>
+      </c>
+      <c r="E215" t="s">
+        <v>13</v>
+      </c>
+      <c r="F215" t="s">
+        <v>14</v>
+      </c>
+      <c r="G215" t="s">
+        <v>15</v>
+      </c>
+      <c r="H215" t="s">
         <v>600</v>
       </c>
-      <c r="C215" t="s">
-        <v>531</v>
-      </c>
-      <c r="D215" t="s">
-        <v>12</v>
-      </c>
-      <c r="E215" t="s">
-        <v>13</v>
-      </c>
-      <c r="F215" t="s">
-        <v>14</v>
-      </c>
-      <c r="G215" t="s">
-        <v>15</v>
-      </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>601</v>
       </c>
-      <c r="I215" t="s">
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>9</v>
-      </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
+        <v>530</v>
+      </c>
+      <c r="D216" t="s">
+        <v>12</v>
+      </c>
+      <c r="E216" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" t="s">
+        <v>14</v>
+      </c>
+      <c r="G216" t="s">
+        <v>15</v>
+      </c>
+      <c r="H216" t="s">
         <v>603</v>
       </c>
-      <c r="C216" t="s">
-        <v>531</v>
-      </c>
-      <c r="D216" t="s">
-        <v>12</v>
-      </c>
-      <c r="E216" t="s">
-        <v>13</v>
-      </c>
-      <c r="F216" t="s">
-        <v>14</v>
-      </c>
-      <c r="G216" t="s">
-        <v>15</v>
-      </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>604</v>
       </c>
-      <c r="I216" t="s">
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>9</v>
+      </c>
+      <c r="B217" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>9</v>
-      </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
+        <v>530</v>
+      </c>
+      <c r="D217" t="s">
+        <v>12</v>
+      </c>
+      <c r="E217" t="s">
+        <v>13</v>
+      </c>
+      <c r="F217" t="s">
+        <v>14</v>
+      </c>
+      <c r="G217" t="s">
+        <v>15</v>
+      </c>
+      <c r="H217" t="s">
         <v>606</v>
       </c>
-      <c r="C217" t="s">
-        <v>531</v>
-      </c>
-      <c r="D217" t="s">
-        <v>12</v>
-      </c>
-      <c r="E217" t="s">
-        <v>13</v>
-      </c>
-      <c r="F217" t="s">
-        <v>14</v>
-      </c>
-      <c r="G217" t="s">
-        <v>15</v>
-      </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>607</v>
       </c>
-      <c r="I217" t="s">
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>9</v>
-      </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
+        <v>530</v>
+      </c>
+      <c r="D218" t="s">
+        <v>12</v>
+      </c>
+      <c r="E218" t="s">
+        <v>13</v>
+      </c>
+      <c r="F218" t="s">
+        <v>14</v>
+      </c>
+      <c r="G218" t="s">
+        <v>15</v>
+      </c>
+      <c r="H218" t="s">
         <v>609</v>
       </c>
-      <c r="C218" t="s">
-        <v>531</v>
-      </c>
-      <c r="D218" t="s">
-        <v>12</v>
-      </c>
-      <c r="E218" t="s">
-        <v>13</v>
-      </c>
-      <c r="F218" t="s">
-        <v>14</v>
-      </c>
-      <c r="G218" t="s">
-        <v>15</v>
-      </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>610</v>
       </c>
-      <c r="I218" t="s">
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>9</v>
+      </c>
+      <c r="B219" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>9</v>
-      </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
+        <v>530</v>
+      </c>
+      <c r="D219" t="s">
+        <v>12</v>
+      </c>
+      <c r="E219" t="s">
+        <v>13</v>
+      </c>
+      <c r="F219" t="s">
+        <v>14</v>
+      </c>
+      <c r="G219" t="s">
+        <v>15</v>
+      </c>
+      <c r="H219" t="s">
         <v>612</v>
       </c>
-      <c r="C219" t="s">
-        <v>531</v>
-      </c>
-      <c r="D219" t="s">
-        <v>12</v>
-      </c>
-      <c r="E219" t="s">
-        <v>13</v>
-      </c>
-      <c r="F219" t="s">
-        <v>14</v>
-      </c>
-      <c r="G219" t="s">
-        <v>15</v>
-      </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>613</v>
       </c>
-      <c r="I219" t="s">
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>9</v>
-      </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
+        <v>530</v>
+      </c>
+      <c r="D220" t="s">
+        <v>12</v>
+      </c>
+      <c r="E220" t="s">
+        <v>13</v>
+      </c>
+      <c r="F220" t="s">
+        <v>14</v>
+      </c>
+      <c r="G220" t="s">
+        <v>15</v>
+      </c>
+      <c r="H220" t="s">
         <v>615</v>
       </c>
-      <c r="C220" t="s">
-        <v>531</v>
-      </c>
-      <c r="D220" t="s">
-        <v>12</v>
-      </c>
-      <c r="E220" t="s">
-        <v>13</v>
-      </c>
-      <c r="F220" t="s">
-        <v>14</v>
-      </c>
-      <c r="G220" t="s">
-        <v>15</v>
-      </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>616</v>
       </c>
-      <c r="I220" t="s">
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>9</v>
+      </c>
+      <c r="B221" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>9</v>
-      </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
+        <v>530</v>
+      </c>
+      <c r="D221" t="s">
+        <v>12</v>
+      </c>
+      <c r="E221" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221" t="s">
+        <v>14</v>
+      </c>
+      <c r="G221" t="s">
+        <v>15</v>
+      </c>
+      <c r="H221" t="s">
         <v>618</v>
       </c>
-      <c r="C221" t="s">
-        <v>531</v>
-      </c>
-      <c r="D221" t="s">
-        <v>12</v>
-      </c>
-      <c r="E221" t="s">
-        <v>13</v>
-      </c>
-      <c r="F221" t="s">
-        <v>14</v>
-      </c>
-      <c r="G221" t="s">
-        <v>15</v>
-      </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>619</v>
       </c>
-      <c r="I221" t="s">
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>9</v>
+      </c>
+      <c r="B222" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>9</v>
-      </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
+        <v>530</v>
+      </c>
+      <c r="D222" t="s">
+        <v>12</v>
+      </c>
+      <c r="E222" t="s">
+        <v>13</v>
+      </c>
+      <c r="F222" t="s">
+        <v>14</v>
+      </c>
+      <c r="G222" t="s">
+        <v>15</v>
+      </c>
+      <c r="H222" t="s">
         <v>621</v>
       </c>
-      <c r="C222" t="s">
-        <v>531</v>
-      </c>
-      <c r="D222" t="s">
-        <v>12</v>
-      </c>
-      <c r="E222" t="s">
-        <v>13</v>
-      </c>
-      <c r="F222" t="s">
-        <v>14</v>
-      </c>
-      <c r="G222" t="s">
-        <v>15</v>
-      </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>622</v>
       </c>
-      <c r="I222" t="s">
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>9</v>
-      </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
+        <v>530</v>
+      </c>
+      <c r="D223" t="s">
+        <v>12</v>
+      </c>
+      <c r="E223" t="s">
+        <v>13</v>
+      </c>
+      <c r="F223" t="s">
+        <v>14</v>
+      </c>
+      <c r="G223" t="s">
+        <v>15</v>
+      </c>
+      <c r="H223" t="s">
         <v>624</v>
       </c>
-      <c r="C223" t="s">
-        <v>531</v>
-      </c>
-      <c r="D223" t="s">
-        <v>12</v>
-      </c>
-      <c r="E223" t="s">
-        <v>13</v>
-      </c>
-      <c r="F223" t="s">
-        <v>14</v>
-      </c>
-      <c r="G223" t="s">
-        <v>15</v>
-      </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>625</v>
       </c>
-      <c r="I223" t="s">
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>9</v>
-      </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
+        <v>530</v>
+      </c>
+      <c r="D224" t="s">
+        <v>12</v>
+      </c>
+      <c r="E224" t="s">
+        <v>13</v>
+      </c>
+      <c r="F224" t="s">
+        <v>14</v>
+      </c>
+      <c r="G224" t="s">
+        <v>15</v>
+      </c>
+      <c r="H224" t="s">
         <v>627</v>
       </c>
-      <c r="C224" t="s">
-        <v>531</v>
-      </c>
-      <c r="D224" t="s">
-        <v>12</v>
-      </c>
-      <c r="E224" t="s">
-        <v>13</v>
-      </c>
-      <c r="F224" t="s">
-        <v>14</v>
-      </c>
-      <c r="G224" t="s">
-        <v>15</v>
-      </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>628</v>
       </c>
-      <c r="I224" t="s">
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>9</v>
+      </c>
+      <c r="B225" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>9</v>
-      </c>
-      <c r="B225" t="s">
+      <c r="C225" t="s">
+        <v>530</v>
+      </c>
+      <c r="D225" t="s">
+        <v>12</v>
+      </c>
+      <c r="E225" t="s">
+        <v>13</v>
+      </c>
+      <c r="F225" t="s">
+        <v>14</v>
+      </c>
+      <c r="G225" t="s">
+        <v>15</v>
+      </c>
+      <c r="H225" t="s">
         <v>630</v>
       </c>
-      <c r="C225" t="s">
-        <v>531</v>
-      </c>
-      <c r="D225" t="s">
-        <v>12</v>
-      </c>
-      <c r="E225" t="s">
-        <v>13</v>
-      </c>
-      <c r="F225" t="s">
-        <v>14</v>
-      </c>
-      <c r="G225" t="s">
-        <v>15</v>
-      </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>631</v>
       </c>
-      <c r="I225" t="s">
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>9</v>
-      </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
+        <v>530</v>
+      </c>
+      <c r="D226" t="s">
+        <v>12</v>
+      </c>
+      <c r="E226" t="s">
+        <v>13</v>
+      </c>
+      <c r="F226" t="s">
+        <v>14</v>
+      </c>
+      <c r="G226" t="s">
+        <v>15</v>
+      </c>
+      <c r="H226" t="s">
         <v>633</v>
       </c>
-      <c r="C226" t="s">
-        <v>531</v>
-      </c>
-      <c r="D226" t="s">
-        <v>12</v>
-      </c>
-      <c r="E226" t="s">
-        <v>13</v>
-      </c>
-      <c r="F226" t="s">
-        <v>14</v>
-      </c>
-      <c r="G226" t="s">
-        <v>15</v>
-      </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>634</v>
       </c>
-      <c r="I226" t="s">
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B227" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>9</v>
-      </c>
-      <c r="B227" t="s">
+      <c r="C227" t="s">
+        <v>530</v>
+      </c>
+      <c r="D227" t="s">
+        <v>12</v>
+      </c>
+      <c r="E227" t="s">
+        <v>13</v>
+      </c>
+      <c r="F227" t="s">
+        <v>14</v>
+      </c>
+      <c r="G227" t="s">
+        <v>15</v>
+      </c>
+      <c r="H227" t="s">
         <v>636</v>
       </c>
-      <c r="C227" t="s">
-        <v>531</v>
-      </c>
-      <c r="D227" t="s">
-        <v>12</v>
-      </c>
-      <c r="E227" t="s">
-        <v>13</v>
-      </c>
-      <c r="F227" t="s">
-        <v>14</v>
-      </c>
-      <c r="G227" t="s">
-        <v>15</v>
-      </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>637</v>
       </c>
-      <c r="I227" t="s">
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>9</v>
-      </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
+        <v>530</v>
+      </c>
+      <c r="D228" t="s">
+        <v>12</v>
+      </c>
+      <c r="E228" t="s">
+        <v>13</v>
+      </c>
+      <c r="F228" t="s">
+        <v>14</v>
+      </c>
+      <c r="G228" t="s">
+        <v>15</v>
+      </c>
+      <c r="H228" t="s">
         <v>639</v>
       </c>
-      <c r="C228" t="s">
-        <v>531</v>
-      </c>
-      <c r="D228" t="s">
-        <v>12</v>
-      </c>
-      <c r="E228" t="s">
-        <v>13</v>
-      </c>
-      <c r="F228" t="s">
-        <v>14</v>
-      </c>
-      <c r="G228" t="s">
-        <v>15</v>
-      </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>640</v>
       </c>
-      <c r="I228" t="s">
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B229" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
-        <v>9</v>
-      </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
+        <v>530</v>
+      </c>
+      <c r="D229" t="s">
+        <v>12</v>
+      </c>
+      <c r="E229" t="s">
+        <v>13</v>
+      </c>
+      <c r="F229" t="s">
+        <v>14</v>
+      </c>
+      <c r="G229" t="s">
+        <v>15</v>
+      </c>
+      <c r="H229" t="s">
         <v>642</v>
       </c>
-      <c r="C229" t="s">
-        <v>531</v>
-      </c>
-      <c r="D229" t="s">
-        <v>12</v>
-      </c>
-      <c r="E229" t="s">
-        <v>13</v>
-      </c>
-      <c r="F229" t="s">
-        <v>14</v>
-      </c>
-      <c r="G229" t="s">
-        <v>15</v>
-      </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>643</v>
       </c>
-      <c r="I229" t="s">
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
-        <v>9</v>
-      </c>
-      <c r="B230" t="s">
+      <c r="C230" t="s">
+        <v>530</v>
+      </c>
+      <c r="D230" t="s">
+        <v>12</v>
+      </c>
+      <c r="E230" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230" t="s">
+        <v>14</v>
+      </c>
+      <c r="G230" t="s">
+        <v>15</v>
+      </c>
+      <c r="H230" t="s">
         <v>645</v>
       </c>
-      <c r="C230" t="s">
-        <v>531</v>
-      </c>
-      <c r="D230" t="s">
-        <v>12</v>
-      </c>
-      <c r="E230" t="s">
-        <v>13</v>
-      </c>
-      <c r="F230" t="s">
-        <v>14</v>
-      </c>
-      <c r="G230" t="s">
-        <v>15</v>
-      </c>
-      <c r="H230" t="s">
+      <c r="I230" t="s">
         <v>646</v>
       </c>
-      <c r="I230" t="s">
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
-        <v>9</v>
-      </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
+        <v>530</v>
+      </c>
+      <c r="D231" t="s">
+        <v>12</v>
+      </c>
+      <c r="E231" t="s">
+        <v>13</v>
+      </c>
+      <c r="F231" t="s">
+        <v>14</v>
+      </c>
+      <c r="G231" t="s">
+        <v>15</v>
+      </c>
+      <c r="H231" t="s">
+        <v>642</v>
+      </c>
+      <c r="I231" t="s">
         <v>648</v>
       </c>
-      <c r="C231" t="s">
-        <v>531</v>
-      </c>
-      <c r="D231" t="s">
-        <v>12</v>
-      </c>
-      <c r="E231" t="s">
-        <v>13</v>
-      </c>
-      <c r="F231" t="s">
-        <v>14</v>
-      </c>
-      <c r="G231" t="s">
-        <v>15</v>
-      </c>
-      <c r="H231" t="s">
-        <v>643</v>
-      </c>
-      <c r="I231" t="s">
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
-        <v>9</v>
-      </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
+        <v>530</v>
+      </c>
+      <c r="D232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E232" t="s">
+        <v>13</v>
+      </c>
+      <c r="F232" t="s">
+        <v>14</v>
+      </c>
+      <c r="G232" t="s">
+        <v>15</v>
+      </c>
+      <c r="H232" t="s">
         <v>650</v>
       </c>
-      <c r="C232" t="s">
-        <v>531</v>
-      </c>
-      <c r="D232" t="s">
-        <v>12</v>
-      </c>
-      <c r="E232" t="s">
-        <v>13</v>
-      </c>
-      <c r="F232" t="s">
-        <v>14</v>
-      </c>
-      <c r="G232" t="s">
-        <v>15</v>
-      </c>
-      <c r="H232" t="s">
+      <c r="I232" t="s">
         <v>651</v>
       </c>
-      <c r="I232" t="s">
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>9</v>
-      </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
+        <v>530</v>
+      </c>
+      <c r="D233" t="s">
+        <v>12</v>
+      </c>
+      <c r="E233" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233" t="s">
+        <v>14</v>
+      </c>
+      <c r="G233" t="s">
+        <v>15</v>
+      </c>
+      <c r="H233" t="s">
         <v>653</v>
       </c>
-      <c r="C233" t="s">
-        <v>531</v>
-      </c>
-      <c r="D233" t="s">
-        <v>12</v>
-      </c>
-      <c r="E233" t="s">
-        <v>13</v>
-      </c>
-      <c r="F233" t="s">
-        <v>14</v>
-      </c>
-      <c r="G233" t="s">
-        <v>15</v>
-      </c>
-      <c r="H233" t="s">
+      <c r="I233" t="s">
         <v>654</v>
       </c>
-      <c r="I233" t="s">
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B234" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
-        <v>9</v>
-      </c>
-      <c r="B234" t="s">
+      <c r="C234" t="s">
+        <v>530</v>
+      </c>
+      <c r="D234" t="s">
+        <v>12</v>
+      </c>
+      <c r="E234" t="s">
+        <v>13</v>
+      </c>
+      <c r="F234" t="s">
+        <v>14</v>
+      </c>
+      <c r="G234" t="s">
+        <v>15</v>
+      </c>
+      <c r="H234" t="s">
         <v>656</v>
       </c>
-      <c r="C234" t="s">
-        <v>531</v>
-      </c>
-      <c r="D234" t="s">
-        <v>12</v>
-      </c>
-      <c r="E234" t="s">
-        <v>13</v>
-      </c>
-      <c r="F234" t="s">
-        <v>14</v>
-      </c>
-      <c r="G234" t="s">
-        <v>15</v>
-      </c>
-      <c r="H234" t="s">
+      <c r="I234" t="s">
         <v>657</v>
       </c>
-      <c r="I234" t="s">
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B235" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>9</v>
-      </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>659</v>
-      </c>
-      <c r="C235" t="s">
-        <v>660</v>
       </c>
       <c r="D235" t="s">
         <v>12</v>
@@ -9907,18 +9907,18 @@
         <v>25</v>
       </c>
       <c r="I235" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>9</v>
-      </c>
-      <c r="B236" t="s">
-        <v>662</v>
-      </c>
       <c r="C236" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D236" t="s">
         <v>12</v>
@@ -9936,18 +9936,18 @@
         <v>28</v>
       </c>
       <c r="I236" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
-        <v>9</v>
-      </c>
-      <c r="B237" t="s">
-        <v>664</v>
-      </c>
       <c r="C237" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D237" t="s">
         <v>12</v>
@@ -9965,18 +9965,18 @@
         <v>31</v>
       </c>
       <c r="I237" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
-        <v>9</v>
-      </c>
-      <c r="B238" t="s">
-        <v>666</v>
-      </c>
       <c r="C238" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D238" t="s">
         <v>12</v>
@@ -9994,18 +9994,18 @@
         <v>34</v>
       </c>
       <c r="I238" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>9</v>
-      </c>
-      <c r="B239" t="s">
-        <v>668</v>
-      </c>
       <c r="C239" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D239" t="s">
         <v>12</v>
@@ -10023,18 +10023,18 @@
         <v>37</v>
       </c>
       <c r="I239" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>9</v>
+      </c>
+      <c r="B240" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
-        <v>9</v>
-      </c>
-      <c r="B240" t="s">
-        <v>670</v>
-      </c>
       <c r="C240" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D240" t="s">
         <v>12</v>
@@ -10052,18 +10052,18 @@
         <v>40</v>
       </c>
       <c r="I240" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
-        <v>9</v>
-      </c>
-      <c r="B241" t="s">
-        <v>672</v>
-      </c>
       <c r="C241" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D241" t="s">
         <v>12</v>
@@ -10081,18 +10081,18 @@
         <v>43</v>
       </c>
       <c r="I241" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
-        <v>9</v>
-      </c>
-      <c r="B242" t="s">
-        <v>674</v>
-      </c>
       <c r="C242" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D242" t="s">
         <v>12</v>
@@ -10110,18 +10110,18 @@
         <v>46</v>
       </c>
       <c r="I242" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A243" t="s">
-        <v>9</v>
-      </c>
-      <c r="B243" t="s">
-        <v>676</v>
-      </c>
       <c r="C243" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D243" t="s">
         <v>12</v>
@@ -10139,18 +10139,18 @@
         <v>49</v>
       </c>
       <c r="I243" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>9</v>
+      </c>
+      <c r="B244" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
-        <v>9</v>
-      </c>
-      <c r="B244" t="s">
-        <v>678</v>
-      </c>
       <c r="C244" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D244" t="s">
         <v>12</v>
@@ -10168,18 +10168,18 @@
         <v>52</v>
       </c>
       <c r="I244" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
-        <v>9</v>
-      </c>
-      <c r="B245" t="s">
-        <v>680</v>
-      </c>
       <c r="C245" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D245" t="s">
         <v>12</v>
@@ -10197,18 +10197,18 @@
         <v>55</v>
       </c>
       <c r="I245" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
-        <v>9</v>
-      </c>
-      <c r="B246" t="s">
-        <v>682</v>
-      </c>
       <c r="C246" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D246" t="s">
         <v>12</v>
@@ -10226,18 +10226,18 @@
         <v>58</v>
       </c>
       <c r="I246" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
-        <v>9</v>
-      </c>
-      <c r="B247" t="s">
-        <v>684</v>
-      </c>
       <c r="C247" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D247" t="s">
         <v>12</v>
@@ -10255,18 +10255,18 @@
         <v>115</v>
       </c>
       <c r="I247" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A248" t="s">
-        <v>9</v>
-      </c>
-      <c r="B248" t="s">
-        <v>686</v>
-      </c>
       <c r="C248" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D248" t="s">
         <v>12</v>
@@ -10284,18 +10284,18 @@
         <v>118</v>
       </c>
       <c r="I248" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B249" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
-        <v>9</v>
-      </c>
-      <c r="B249" t="s">
-        <v>688</v>
-      </c>
       <c r="C249" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D249" t="s">
         <v>12</v>
@@ -10313,18 +10313,18 @@
         <v>121</v>
       </c>
       <c r="I249" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B250" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
-        <v>9</v>
-      </c>
-      <c r="B250" t="s">
-        <v>690</v>
-      </c>
       <c r="C250" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D250" t="s">
         <v>12</v>
@@ -10342,18 +10342,18 @@
         <v>124</v>
       </c>
       <c r="I250" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B251" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
-        <v>9</v>
-      </c>
-      <c r="B251" t="s">
-        <v>692</v>
-      </c>
       <c r="C251" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D251" t="s">
         <v>12</v>
@@ -10371,18 +10371,18 @@
         <v>127</v>
       </c>
       <c r="I251" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B252" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
-        <v>9</v>
-      </c>
-      <c r="B252" t="s">
-        <v>694</v>
-      </c>
       <c r="C252" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D252" t="s">
         <v>12</v>
@@ -10400,18 +10400,18 @@
         <v>130</v>
       </c>
       <c r="I252" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
-        <v>9</v>
-      </c>
-      <c r="B253" t="s">
-        <v>696</v>
-      </c>
       <c r="C253" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D253" t="s">
         <v>12</v>
@@ -10429,18 +10429,18 @@
         <v>172</v>
       </c>
       <c r="I253" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
-        <v>9</v>
-      </c>
-      <c r="B254" t="s">
-        <v>698</v>
-      </c>
       <c r="C254" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D254" t="s">
         <v>12</v>
@@ -10458,18 +10458,18 @@
         <v>175</v>
       </c>
       <c r="I254" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
-        <v>9</v>
-      </c>
-      <c r="B255" t="s">
-        <v>700</v>
-      </c>
       <c r="C255" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D255" t="s">
         <v>12</v>
@@ -10487,18 +10487,18 @@
         <v>178</v>
       </c>
       <c r="I255" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
-        <v>9</v>
-      </c>
-      <c r="B256" t="s">
-        <v>702</v>
-      </c>
       <c r="C256" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D256" t="s">
         <v>12</v>
@@ -10516,18 +10516,18 @@
         <v>181</v>
       </c>
       <c r="I256" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
-        <v>9</v>
-      </c>
-      <c r="B257" t="s">
-        <v>704</v>
-      </c>
       <c r="C257" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D257" t="s">
         <v>12</v>
@@ -10545,18 +10545,18 @@
         <v>184</v>
       </c>
       <c r="I257" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
-        <v>9</v>
-      </c>
-      <c r="B258" t="s">
-        <v>706</v>
-      </c>
       <c r="C258" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D258" t="s">
         <v>12</v>
@@ -10574,47 +10574,47 @@
         <v>187</v>
       </c>
       <c r="I258" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
-        <v>9</v>
-      </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
+        <v>659</v>
+      </c>
+      <c r="D259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
+        <v>13</v>
+      </c>
+      <c r="F259" t="s">
+        <v>14</v>
+      </c>
+      <c r="G259" t="s">
+        <v>15</v>
+      </c>
+      <c r="H259" t="s">
         <v>708</v>
       </c>
-      <c r="C259" t="s">
-        <v>660</v>
-      </c>
-      <c r="D259" t="s">
-        <v>12</v>
-      </c>
-      <c r="E259" t="s">
-        <v>13</v>
-      </c>
-      <c r="F259" t="s">
-        <v>14</v>
-      </c>
-      <c r="G259" t="s">
-        <v>15</v>
-      </c>
-      <c r="H259" t="s">
+      <c r="I259" t="s">
         <v>709</v>
       </c>
-      <c r="I259" t="s">
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A260" t="s">
-        <v>9</v>
-      </c>
-      <c r="B260" t="s">
-        <v>711</v>
-      </c>
       <c r="C260" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D260" t="s">
         <v>12</v>
@@ -10632,76 +10632,76 @@
         <v>211</v>
       </c>
       <c r="I260" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B261" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
-        <v>9</v>
-      </c>
-      <c r="B261" t="s">
+      <c r="C261" t="s">
+        <v>659</v>
+      </c>
+      <c r="D261" t="s">
+        <v>12</v>
+      </c>
+      <c r="E261" t="s">
+        <v>13</v>
+      </c>
+      <c r="F261" t="s">
+        <v>14</v>
+      </c>
+      <c r="G261" t="s">
+        <v>15</v>
+      </c>
+      <c r="H261" t="s">
         <v>713</v>
       </c>
-      <c r="C261" t="s">
-        <v>660</v>
-      </c>
-      <c r="D261" t="s">
-        <v>12</v>
-      </c>
-      <c r="E261" t="s">
-        <v>13</v>
-      </c>
-      <c r="F261" t="s">
-        <v>14</v>
-      </c>
-      <c r="G261" t="s">
-        <v>15</v>
-      </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
         <v>714</v>
-      </c>
-      <c r="I261" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B262" t="s">
+        <v>715</v>
+      </c>
+      <c r="C262" t="s">
         <v>716</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
+        <v>12</v>
+      </c>
+      <c r="E262" t="s">
+        <v>13</v>
+      </c>
+      <c r="F262" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262" t="s">
+        <v>15</v>
+      </c>
+      <c r="H262" t="s">
         <v>717</v>
       </c>
-      <c r="D262" t="s">
-        <v>12</v>
-      </c>
-      <c r="E262" t="s">
-        <v>13</v>
-      </c>
-      <c r="F262" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" t="s">
-        <v>15</v>
-      </c>
-      <c r="H262" t="s">
+      <c r="I262" t="s">
         <v>718</v>
-      </c>
-      <c r="I262" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B263" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C263" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D263" t="s">
         <v>12</v>
@@ -10719,18 +10719,18 @@
         <v>16</v>
       </c>
       <c r="I263" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B264" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C264" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D264" t="s">
         <v>12</v>
@@ -10748,18 +10748,18 @@
         <v>19</v>
       </c>
       <c r="I264" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B265" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C265" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D265" t="s">
         <v>12</v>
@@ -10777,18 +10777,18 @@
         <v>22</v>
       </c>
       <c r="I265" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B266" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C266" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D266" t="s">
         <v>12</v>
@@ -10806,18 +10806,18 @@
         <v>25</v>
       </c>
       <c r="I266" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B267" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C267" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D267" t="s">
         <v>12</v>
@@ -10835,18 +10835,18 @@
         <v>28</v>
       </c>
       <c r="I267" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B268" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C268" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D268" t="s">
         <v>12</v>
@@ -10864,18 +10864,18 @@
         <v>31</v>
       </c>
       <c r="I268" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B269" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C269" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D269" t="s">
         <v>12</v>
@@ -10893,18 +10893,18 @@
         <v>34</v>
       </c>
       <c r="I269" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B270" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C270" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D270" t="s">
         <v>12</v>
@@ -10922,18 +10922,18 @@
         <v>37</v>
       </c>
       <c r="I270" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B271" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C271" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D271" t="s">
         <v>12</v>
@@ -10951,18 +10951,18 @@
         <v>40</v>
       </c>
       <c r="I271" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B272" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C272" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D272" t="s">
         <v>12</v>
@@ -10980,18 +10980,18 @@
         <v>43</v>
       </c>
       <c r="I272" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C273" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D273" t="s">
         <v>12</v>
@@ -11009,18 +11009,18 @@
         <v>46</v>
       </c>
       <c r="I273" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B274" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C274" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D274" t="s">
         <v>12</v>
@@ -11038,18 +11038,18 @@
         <v>49</v>
       </c>
       <c r="I274" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B275" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C275" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D275" t="s">
         <v>12</v>
@@ -11067,18 +11067,18 @@
         <v>52</v>
       </c>
       <c r="I275" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B276" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C276" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D276" t="s">
         <v>12</v>
@@ -11096,18 +11096,18 @@
         <v>55</v>
       </c>
       <c r="I276" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B277" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C277" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D277" t="s">
         <v>12</v>
@@ -11125,47 +11125,47 @@
         <v>58</v>
       </c>
       <c r="I277" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B278" t="s">
+        <v>749</v>
+      </c>
+      <c r="C278" t="s">
+        <v>716</v>
+      </c>
+      <c r="D278" t="s">
+        <v>12</v>
+      </c>
+      <c r="E278" t="s">
+        <v>13</v>
+      </c>
+      <c r="F278" t="s">
+        <v>14</v>
+      </c>
+      <c r="G278" t="s">
+        <v>15</v>
+      </c>
+      <c r="H278" t="s">
         <v>750</v>
       </c>
-      <c r="C278" t="s">
-        <v>717</v>
-      </c>
-      <c r="D278" t="s">
-        <v>12</v>
-      </c>
-      <c r="E278" t="s">
-        <v>13</v>
-      </c>
-      <c r="F278" t="s">
-        <v>14</v>
-      </c>
-      <c r="G278" t="s">
-        <v>15</v>
-      </c>
-      <c r="H278" t="s">
+      <c r="I278" t="s">
         <v>751</v>
-      </c>
-      <c r="I278" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B279" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C279" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D279" t="s">
         <v>12</v>
@@ -11183,47 +11183,47 @@
         <v>82</v>
       </c>
       <c r="I279" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B280" t="s">
+        <v>754</v>
+      </c>
+      <c r="C280" t="s">
+        <v>716</v>
+      </c>
+      <c r="D280" t="s">
+        <v>12</v>
+      </c>
+      <c r="E280" t="s">
+        <v>13</v>
+      </c>
+      <c r="F280" t="s">
+        <v>14</v>
+      </c>
+      <c r="G280" t="s">
+        <v>15</v>
+      </c>
+      <c r="H280" t="s">
         <v>755</v>
       </c>
-      <c r="C280" t="s">
-        <v>717</v>
-      </c>
-      <c r="D280" t="s">
-        <v>12</v>
-      </c>
-      <c r="E280" t="s">
-        <v>13</v>
-      </c>
-      <c r="F280" t="s">
-        <v>14</v>
-      </c>
-      <c r="G280" t="s">
-        <v>15</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="I280" t="s">
         <v>756</v>
-      </c>
-      <c r="I280" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B281" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C281" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D281" t="s">
         <v>12</v>
@@ -11241,18 +11241,18 @@
         <v>88</v>
       </c>
       <c r="I281" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B282" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C282" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D282" t="s">
         <v>12</v>
@@ -11270,18 +11270,18 @@
         <v>91</v>
       </c>
       <c r="I282" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B283" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C283" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D283" t="s">
         <v>12</v>
@@ -11299,18 +11299,18 @@
         <v>94</v>
       </c>
       <c r="I283" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C284" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D284" t="s">
         <v>12</v>
@@ -11328,18 +11328,18 @@
         <v>97</v>
       </c>
       <c r="I284" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C285" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D285" t="s">
         <v>12</v>
@@ -11357,18 +11357,18 @@
         <v>100</v>
       </c>
       <c r="I285" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C286" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D286" t="s">
         <v>12</v>
@@ -11386,18 +11386,18 @@
         <v>106</v>
       </c>
       <c r="I286" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C287" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D287" t="s">
         <v>12</v>
@@ -11415,18 +11415,18 @@
         <v>109</v>
       </c>
       <c r="I287" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C288" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D288" t="s">
         <v>12</v>
@@ -11444,18 +11444,18 @@
         <v>112</v>
       </c>
       <c r="I288" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C289" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D289" t="s">
         <v>12</v>
@@ -11473,18 +11473,18 @@
         <v>115</v>
       </c>
       <c r="I289" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C290" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D290" t="s">
         <v>12</v>
@@ -11502,18 +11502,18 @@
         <v>118</v>
       </c>
       <c r="I290" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B291" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C291" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D291" t="s">
         <v>12</v>
@@ -11531,18 +11531,18 @@
         <v>121</v>
       </c>
       <c r="I291" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B292" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C292" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D292" t="s">
         <v>12</v>
@@ -11560,18 +11560,18 @@
         <v>124</v>
       </c>
       <c r="I292" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B293" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C293" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D293" t="s">
         <v>12</v>
@@ -11589,18 +11589,18 @@
         <v>127</v>
       </c>
       <c r="I293" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B294" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C294" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D294" t="s">
         <v>12</v>
@@ -11618,18 +11618,18 @@
         <v>130</v>
       </c>
       <c r="I294" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B295" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C295" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D295" t="s">
         <v>12</v>
@@ -11647,18 +11647,18 @@
         <v>145</v>
       </c>
       <c r="I295" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B296" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C296" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D296" t="s">
         <v>12</v>
@@ -11676,18 +11676,18 @@
         <v>147</v>
       </c>
       <c r="I296" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B297" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C297" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D297" t="s">
         <v>12</v>
@@ -11705,18 +11705,18 @@
         <v>149</v>
       </c>
       <c r="I297" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C298" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D298" t="s">
         <v>12</v>
@@ -11734,18 +11734,18 @@
         <v>151</v>
       </c>
       <c r="I298" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B299" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C299" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D299" t="s">
         <v>12</v>
@@ -11763,18 +11763,18 @@
         <v>153</v>
       </c>
       <c r="I299" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B300" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C300" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D300" t="s">
         <v>12</v>
@@ -11792,18 +11792,18 @@
         <v>163</v>
       </c>
       <c r="I300" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B301" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C301" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D301" t="s">
         <v>12</v>
@@ -11821,18 +11821,18 @@
         <v>166</v>
       </c>
       <c r="I301" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B302" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C302" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D302" t="s">
         <v>12</v>
@@ -11850,18 +11850,18 @@
         <v>169</v>
       </c>
       <c r="I302" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B303" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C303" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D303" t="s">
         <v>12</v>
@@ -11879,18 +11879,18 @@
         <v>172</v>
       </c>
       <c r="I303" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B304" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C304" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D304" t="s">
         <v>12</v>
@@ -11908,47 +11908,47 @@
         <v>175</v>
       </c>
       <c r="I304" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B305" t="s">
+        <v>805</v>
+      </c>
+      <c r="C305" t="s">
+        <v>716</v>
+      </c>
+      <c r="D305" t="s">
+        <v>12</v>
+      </c>
+      <c r="E305" t="s">
+        <v>13</v>
+      </c>
+      <c r="F305" t="s">
+        <v>14</v>
+      </c>
+      <c r="G305" t="s">
+        <v>15</v>
+      </c>
+      <c r="H305" t="s">
         <v>806</v>
       </c>
-      <c r="C305" t="s">
-        <v>717</v>
-      </c>
-      <c r="D305" t="s">
-        <v>12</v>
-      </c>
-      <c r="E305" t="s">
-        <v>13</v>
-      </c>
-      <c r="F305" t="s">
-        <v>14</v>
-      </c>
-      <c r="G305" t="s">
-        <v>15</v>
-      </c>
-      <c r="H305" t="s">
+      <c r="I305" t="s">
         <v>807</v>
-      </c>
-      <c r="I305" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B306" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C306" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D306" t="s">
         <v>12</v>
@@ -11966,18 +11966,18 @@
         <v>181</v>
       </c>
       <c r="I306" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B307" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C307" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D307" t="s">
         <v>12</v>
@@ -11995,18 +11995,18 @@
         <v>184</v>
       </c>
       <c r="I307" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B308" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C308" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D308" t="s">
         <v>12</v>
@@ -12024,47 +12024,47 @@
         <v>187</v>
       </c>
       <c r="I308" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B309" t="s">
+        <v>814</v>
+      </c>
+      <c r="C309" t="s">
+        <v>716</v>
+      </c>
+      <c r="D309" t="s">
+        <v>12</v>
+      </c>
+      <c r="E309" t="s">
+        <v>13</v>
+      </c>
+      <c r="F309" t="s">
+        <v>14</v>
+      </c>
+      <c r="G309" t="s">
+        <v>15</v>
+      </c>
+      <c r="H309" t="s">
+        <v>708</v>
+      </c>
+      <c r="I309" t="s">
         <v>815</v>
-      </c>
-      <c r="C309" t="s">
-        <v>717</v>
-      </c>
-      <c r="D309" t="s">
-        <v>12</v>
-      </c>
-      <c r="E309" t="s">
-        <v>13</v>
-      </c>
-      <c r="F309" t="s">
-        <v>14</v>
-      </c>
-      <c r="G309" t="s">
-        <v>15</v>
-      </c>
-      <c r="H309" t="s">
-        <v>709</v>
-      </c>
-      <c r="I309" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B310" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C310" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D310" t="s">
         <v>12</v>
@@ -12082,47 +12082,47 @@
         <v>211</v>
       </c>
       <c r="I310" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B311" t="s">
+        <v>818</v>
+      </c>
+      <c r="C311" t="s">
+        <v>716</v>
+      </c>
+      <c r="D311" t="s">
+        <v>12</v>
+      </c>
+      <c r="E311" t="s">
+        <v>13</v>
+      </c>
+      <c r="F311" t="s">
+        <v>14</v>
+      </c>
+      <c r="G311" t="s">
+        <v>15</v>
+      </c>
+      <c r="H311" t="s">
+        <v>713</v>
+      </c>
+      <c r="I311" t="s">
         <v>819</v>
-      </c>
-      <c r="C311" t="s">
-        <v>717</v>
-      </c>
-      <c r="D311" t="s">
-        <v>12</v>
-      </c>
-      <c r="E311" t="s">
-        <v>13</v>
-      </c>
-      <c r="F311" t="s">
-        <v>14</v>
-      </c>
-      <c r="G311" t="s">
-        <v>15</v>
-      </c>
-      <c r="H311" t="s">
-        <v>714</v>
-      </c>
-      <c r="I311" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B312" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C312" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D312" t="s">
         <v>12</v>
@@ -12140,18 +12140,18 @@
         <v>217</v>
       </c>
       <c r="I312" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B313" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C313" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D313" t="s">
         <v>12</v>
@@ -12169,18 +12169,18 @@
         <v>220</v>
       </c>
       <c r="I313" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B314" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C314" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D314" t="s">
         <v>12</v>
@@ -12198,18 +12198,18 @@
         <v>223</v>
       </c>
       <c r="I314" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B315" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C315" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D315" t="s">
         <v>12</v>
@@ -12227,18 +12227,18 @@
         <v>226</v>
       </c>
       <c r="I315" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B316" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C316" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D316" t="s">
         <v>12</v>
@@ -12256,18 +12256,18 @@
         <v>229</v>
       </c>
       <c r="I316" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B317" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C317" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D317" s="2">
         <v>2027</v>
@@ -12282,21 +12282,21 @@
         <v>15</v>
       </c>
       <c r="H317" t="s">
+        <v>831</v>
+      </c>
+      <c r="I317" t="s">
         <v>832</v>
-      </c>
-      <c r="I317" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B318" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C318" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D318" s="2">
         <v>2027</v>
@@ -12311,21 +12311,21 @@
         <v>15</v>
       </c>
       <c r="H318" t="s">
+        <v>834</v>
+      </c>
+      <c r="I318" t="s">
         <v>835</v>
-      </c>
-      <c r="I318" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C319" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D319" s="2">
         <v>2027</v>
@@ -12340,21 +12340,21 @@
         <v>15</v>
       </c>
       <c r="H319" t="s">
+        <v>837</v>
+      </c>
+      <c r="I319" t="s">
         <v>838</v>
-      </c>
-      <c r="I319" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C320" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D320" s="2">
         <v>2027</v>
@@ -12369,21 +12369,21 @@
         <v>15</v>
       </c>
       <c r="H320" t="s">
+        <v>840</v>
+      </c>
+      <c r="I320" t="s">
         <v>841</v>
-      </c>
-      <c r="I320" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C321" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D321" s="2">
         <v>2027</v>
@@ -12398,21 +12398,21 @@
         <v>15</v>
       </c>
       <c r="H321" t="s">
+        <v>843</v>
+      </c>
+      <c r="I321" t="s">
         <v>844</v>
-      </c>
-      <c r="I321" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C322" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D322" s="2">
         <v>2027</v>
@@ -12427,21 +12427,21 @@
         <v>15</v>
       </c>
       <c r="H322" t="s">
+        <v>846</v>
+      </c>
+      <c r="I322" t="s">
         <v>847</v>
-      </c>
-      <c r="I322" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C323" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D323" s="2">
         <v>2027</v>
@@ -12456,21 +12456,21 @@
         <v>15</v>
       </c>
       <c r="H323" t="s">
+        <v>849</v>
+      </c>
+      <c r="I323" t="s">
         <v>850</v>
-      </c>
-      <c r="I323" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C324" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D324" s="2">
         <v>2027</v>
@@ -12485,21 +12485,21 @@
         <v>15</v>
       </c>
       <c r="H324" t="s">
+        <v>852</v>
+      </c>
+      <c r="I324" t="s">
         <v>853</v>
-      </c>
-      <c r="I324" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C325" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D325" s="2">
         <v>2027</v>
@@ -12514,21 +12514,21 @@
         <v>15</v>
       </c>
       <c r="H325" t="s">
+        <v>855</v>
+      </c>
+      <c r="I325" t="s">
         <v>856</v>
-      </c>
-      <c r="I325" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B326" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C326" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D326" s="2">
         <v>2027</v>
@@ -12543,21 +12543,21 @@
         <v>15</v>
       </c>
       <c r="H326" t="s">
+        <v>858</v>
+      </c>
+      <c r="I326" t="s">
         <v>859</v>
-      </c>
-      <c r="I326" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B327" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C327" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D327" s="2">
         <v>2027</v>
@@ -12575,18 +12575,18 @@
         <v>141</v>
       </c>
       <c r="I327" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>356</v>
+        <v>9</v>
       </c>
       <c r="B328" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C328" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D328" s="2">
         <v>2027</v>
@@ -12601,21 +12601,21 @@
         <v>15</v>
       </c>
       <c r="H328" t="s">
+        <v>863</v>
+      </c>
+      <c r="I328" t="s">
         <v>864</v>
       </c>
-      <c r="I328" t="s">
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A329" t="s">
-        <v>9</v>
-      </c>
-      <c r="B329" t="s">
+      <c r="C329" t="s">
         <v>866</v>
-      </c>
-      <c r="C329" t="s">
-        <v>867</v>
       </c>
       <c r="D329" t="s">
         <v>12</v>
@@ -12633,18 +12633,18 @@
         <v>106</v>
       </c>
       <c r="I329" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>9</v>
+      </c>
+      <c r="B330" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
-        <v>9</v>
-      </c>
-      <c r="B330" t="s">
-        <v>869</v>
-      </c>
       <c r="C330" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D330" t="s">
         <v>12</v>
@@ -12662,18 +12662,18 @@
         <v>109</v>
       </c>
       <c r="I330" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>9</v>
+      </c>
+      <c r="B331" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
-        <v>9</v>
-      </c>
-      <c r="B331" t="s">
-        <v>871</v>
-      </c>
       <c r="C331" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D331" t="s">
         <v>12</v>
@@ -12691,18 +12691,18 @@
         <v>112</v>
       </c>
       <c r="I331" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>9</v>
+      </c>
+      <c r="B332" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A332" t="s">
-        <v>9</v>
-      </c>
-      <c r="B332" t="s">
-        <v>873</v>
-      </c>
       <c r="C332" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D332" t="s">
         <v>12</v>
@@ -12720,18 +12720,18 @@
         <v>115</v>
       </c>
       <c r="I332" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A333" t="s">
-        <v>9</v>
-      </c>
-      <c r="B333" t="s">
-        <v>875</v>
-      </c>
       <c r="C333" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D333" t="s">
         <v>12</v>
@@ -12749,18 +12749,18 @@
         <v>118</v>
       </c>
       <c r="I333" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A334" t="s">
-        <v>9</v>
-      </c>
-      <c r="B334" t="s">
-        <v>877</v>
-      </c>
       <c r="C334" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D334" t="s">
         <v>12</v>
@@ -12778,18 +12778,18 @@
         <v>121</v>
       </c>
       <c r="I334" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A335" t="s">
-        <v>9</v>
-      </c>
-      <c r="B335" t="s">
-        <v>879</v>
-      </c>
       <c r="C335" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D335" t="s">
         <v>12</v>
@@ -12807,18 +12807,18 @@
         <v>124</v>
       </c>
       <c r="I335" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A336" t="s">
-        <v>9</v>
-      </c>
-      <c r="B336" t="s">
-        <v>881</v>
-      </c>
       <c r="C336" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D336" t="s">
         <v>12</v>
@@ -12836,18 +12836,18 @@
         <v>127</v>
       </c>
       <c r="I336" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
-        <v>9</v>
-      </c>
-      <c r="B337" t="s">
-        <v>883</v>
-      </c>
       <c r="C337" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D337" t="s">
         <v>12</v>
@@ -12865,20 +12865,14 @@
         <v>130</v>
       </c>
       <c r="I337" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I337" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="TX"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I337" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I88 A152:I158 B123:I147 B166:I169 B163:I163 B164:I165 B173:I176 B170:I172 B180:I184 B177:I179 A192:I261 B185:I187 B188:I191 B266:I269 B262:I262 B263:I265 B274:I277 B270:I273 B282:I285 B278:I281 B290:I293 B286:I289 B298:I301 B294:I297 B306:I309 B302:I305 B314:I317 B310:I313 A329:I331 B318:I321 B322:I328 A93:I96 B89:I89 B90:I92 A101:I104 B97:I100 A109:I112 B105:I108 A117:I122 B113:I116 B148:I151 B159:I162 A336:I337 B332:I335" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I2 B152:I158 B123:I147 B166:I169 B163:I163 B164:I165 B173:I176 B170:I172 B180:I184 B177:I179 B192:I261 B185:I187 B188:I191 B266:I269 B262:I262 B263:I265 B274:I277 B270:I273 B282:I285 B278:I281 B290:I293 B286:I289 B298:I301 B294:I297 B306:I309 B302:I305 B314:I317 B310:I313 B330:I331 B318:I321 B322:I328 B93:I96 B89:I89 B90:I92 B101:I104 B97:I100 B109:I112 B105:I108 B117:I122 B113:I116 B148:I151 B159:I162 B336:I337 B332:I335 B329:I329 B3:I88" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12893,24 +12887,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B1" t="s">
         <v>885</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>886</v>
-      </c>
-      <c r="C1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="C2" t="s">
         <v>888</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="C2" t="s">
-        <v>889</v>
       </c>
     </row>
   </sheetData>
